--- a/data/《视频点位确认表》 0620.xlsx
+++ b/data/《视频点位确认表》 0620.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="视频点位" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="轮询视频列表（路产路权） " sheetId="17" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">视频点位!$A$1:$G$640</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">视频点位!$F$1:$F$640</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'轮询视频列表（路产路权） '!$A$132:$G$195</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,10 +32,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1962,13 +1958,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
@@ -2226,9 +2215,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:XEZ640"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="6.625" style="18" customWidth="1"/>
     <col min="2" max="2" width="22.975" style="19" customWidth="1"/>
@@ -2244,7 +2233,7 @@
     <col min="13" max="16383" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" spans="1:16380">
+    <row r="1" ht="37.5" spans="1:16380">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -2271,7 +2260,7 @@
       <c r="L1" s="18"/>
       <c r="XEZ1"/>
     </row>
-    <row r="2" ht="35" spans="1:16380">
+    <row r="2" ht="37.5" spans="1:16380">
       <c r="A2" s="4">
         <f>COUNTA($A$1:A1)</f>
         <v>1</v>
@@ -2299,7 +2288,7 @@
       <c r="L2" s="18"/>
       <c r="XEZ2"/>
     </row>
-    <row r="3" ht="35" spans="1:16380">
+    <row r="3" ht="37.5" spans="1:16380">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2318,7 +2307,7 @@
       <c r="L3" s="18"/>
       <c r="XEZ3"/>
     </row>
-    <row r="4" ht="52.5" spans="1:16380">
+    <row r="4" ht="56.25" spans="1:16380">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -2337,7 +2326,7 @@
       <c r="L4" s="18"/>
       <c r="XEZ4"/>
     </row>
-    <row r="5" ht="35" spans="1:16380">
+    <row r="5" ht="37.5" spans="1:16380">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2356,7 +2345,7 @@
       <c r="L5" s="18"/>
       <c r="XEZ5"/>
     </row>
-    <row r="6" ht="35" spans="1:16380">
+    <row r="6" ht="37.5" spans="1:16380">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -2394,7 +2383,7 @@
       <c r="L7" s="18"/>
       <c r="XEZ7"/>
     </row>
-    <row r="8" spans="1:16380">
+    <row r="8" hidden="1" spans="1:16380">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2413,7 +2402,7 @@
       <c r="L8" s="18"/>
       <c r="XEZ8"/>
     </row>
-    <row r="9" ht="35" spans="1:16380">
+    <row r="9" ht="37.5" spans="1:16380">
       <c r="A9" s="4">
         <f>COUNTA($A$1:A8)</f>
         <v>2</v>
@@ -2441,7 +2430,7 @@
       <c r="L9" s="18"/>
       <c r="XEZ9"/>
     </row>
-    <row r="10" ht="35" spans="1:16380">
+    <row r="10" ht="37.5" spans="1:16380">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2460,7 +2449,7 @@
       <c r="L10" s="18"/>
       <c r="XEZ10"/>
     </row>
-    <row r="11" ht="52.5" spans="1:16380">
+    <row r="11" ht="56.25" spans="1:16380">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -2479,7 +2468,7 @@
       <c r="L11" s="18"/>
       <c r="XEZ11"/>
     </row>
-    <row r="12" ht="35" spans="1:16380">
+    <row r="12" ht="37.5" spans="1:16380">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -2498,7 +2487,7 @@
       <c r="L12" s="18"/>
       <c r="XEZ12"/>
     </row>
-    <row r="13" ht="35" spans="1:16380">
+    <row r="13" ht="37.5" hidden="1" spans="1:16380">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -2536,7 +2525,7 @@
       <c r="L14" s="18"/>
       <c r="XEZ14"/>
     </row>
-    <row r="15" spans="1:16380">
+    <row r="15" hidden="1" spans="1:16380">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2555,7 +2544,7 @@
       <c r="L15" s="18"/>
       <c r="XEZ15"/>
     </row>
-    <row r="16" ht="35" spans="1:16380">
+    <row r="16" ht="37.5" spans="1:16380">
       <c r="A16" s="4">
         <f>COUNTA($A$1:A15)</f>
         <v>3</v>
@@ -2583,7 +2572,7 @@
       <c r="L16" s="18"/>
       <c r="XEZ16"/>
     </row>
-    <row r="17" ht="35" spans="1:16380">
+    <row r="17" ht="37.5" spans="1:16380">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -2602,7 +2591,7 @@
       <c r="L17" s="18"/>
       <c r="XEZ17"/>
     </row>
-    <row r="18" ht="52.5" spans="1:16380">
+    <row r="18" ht="56.25" spans="1:16380">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -2621,7 +2610,7 @@
       <c r="L18" s="18"/>
       <c r="XEZ18"/>
     </row>
-    <row r="19" ht="35" spans="1:16380">
+    <row r="19" ht="37.5" spans="1:16380">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -2640,7 +2629,7 @@
       <c r="L19" s="18"/>
       <c r="XEZ19"/>
     </row>
-    <row r="20" ht="35" spans="1:16380">
+    <row r="20" ht="37.5" hidden="1" spans="1:16380">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -2678,7 +2667,7 @@
       <c r="L21" s="18"/>
       <c r="XEZ21"/>
     </row>
-    <row r="22" spans="1:16380">
+    <row r="22" hidden="1" spans="1:16380">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -2697,7 +2686,7 @@
       <c r="L22" s="18"/>
       <c r="XEZ22"/>
     </row>
-    <row r="23" ht="35" spans="1:16380">
+    <row r="23" ht="37.5" spans="1:16380">
       <c r="A23" s="4">
         <f>COUNTA($A$1:A22)</f>
         <v>4</v>
@@ -2725,7 +2714,7 @@
       <c r="L23" s="18"/>
       <c r="XEZ23"/>
     </row>
-    <row r="24" ht="35" spans="1:16380">
+    <row r="24" ht="37.5" spans="1:16380">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -2744,7 +2733,7 @@
       <c r="L24" s="18"/>
       <c r="XEZ24"/>
     </row>
-    <row r="25" ht="52.5" spans="1:16380">
+    <row r="25" ht="56.25" spans="1:16380">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -2763,7 +2752,7 @@
       <c r="L25" s="18"/>
       <c r="XEZ25"/>
     </row>
-    <row r="26" ht="35" spans="1:16380">
+    <row r="26" ht="37.5" spans="1:16380">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -2782,7 +2771,7 @@
       <c r="L26" s="18"/>
       <c r="XEZ26"/>
     </row>
-    <row r="27" ht="35" spans="1:16380">
+    <row r="27" ht="37.5" spans="1:16380">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -2820,7 +2809,7 @@
       <c r="L28" s="18"/>
       <c r="XEZ28"/>
     </row>
-    <row r="29" spans="1:16380">
+    <row r="29" hidden="1" spans="1:16380">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -2839,7 +2828,7 @@
       <c r="L29" s="18"/>
       <c r="XEZ29"/>
     </row>
-    <row r="30" ht="35" spans="1:16380">
+    <row r="30" ht="37.5" hidden="1" spans="1:16380">
       <c r="A30" s="4">
         <f>COUNTA($A$1:A29)</f>
         <v>5</v>
@@ -2867,7 +2856,7 @@
       <c r="L30" s="18"/>
       <c r="XEZ30"/>
     </row>
-    <row r="31" ht="35" spans="1:16380">
+    <row r="31" ht="37.5" spans="1:16380">
       <c r="A31" s="4">
         <f>COUNTA($A$1:A30)</f>
         <v>6</v>
@@ -2895,7 +2884,7 @@
       <c r="L31" s="18"/>
       <c r="XEZ31"/>
     </row>
-    <row r="32" ht="35" spans="1:16380">
+    <row r="32" ht="37.5" spans="1:16380">
       <c r="A32" s="4">
         <f>COUNTA($A$1:A31)</f>
         <v>7</v>
@@ -2923,7 +2912,7 @@
       <c r="L32" s="18"/>
       <c r="XEZ32"/>
     </row>
-    <row r="33" customFormat="1" ht="35" spans="1:8">
+    <row r="33" customFormat="1" ht="37.5" spans="1:8">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -2939,7 +2928,7 @@
       </c>
       <c r="H33" s="23"/>
     </row>
-    <row r="34" spans="1:16380">
+    <row r="34" hidden="1" spans="1:16380">
       <c r="A34" s="4">
         <f>COUNTA($A$1:A32)</f>
         <v>8</v>
@@ -2967,7 +2956,7 @@
       <c r="L34" s="18"/>
       <c r="XEZ34"/>
     </row>
-    <row r="35" ht="35" spans="1:16380">
+    <row r="35" ht="37.5" spans="1:16380">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -3014,7 +3003,7 @@
       <c r="L36" s="18"/>
       <c r="XEZ36"/>
     </row>
-    <row r="37" ht="52.5" spans="1:16380">
+    <row r="37" ht="56.25" spans="1:16380">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -3033,7 +3022,7 @@
       <c r="L37" s="18"/>
       <c r="XEZ37"/>
     </row>
-    <row r="38" ht="35" spans="1:16380">
+    <row r="38" ht="37.5" spans="1:16380">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -3052,7 +3041,7 @@
       <c r="L38" s="18"/>
       <c r="XEZ38"/>
     </row>
-    <row r="39" ht="35" spans="1:16380">
+    <row r="39" ht="37.5" spans="1:16380">
       <c r="A39" s="4">
         <f>COUNTA($A$1:A38)</f>
         <v>10</v>
@@ -3080,7 +3069,7 @@
       <c r="L39" s="18"/>
       <c r="XEZ39"/>
     </row>
-    <row r="40" ht="52.5" spans="1:16380">
+    <row r="40" ht="56.25" spans="1:16380">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -3099,7 +3088,7 @@
       <c r="L40" s="18"/>
       <c r="XEZ40"/>
     </row>
-    <row r="41" ht="35" spans="1:16380">
+    <row r="41" ht="37.5" hidden="1" spans="1:16380">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -3118,7 +3107,7 @@
       <c r="L41" s="18"/>
       <c r="XEZ41"/>
     </row>
-    <row r="42" ht="35" spans="1:16380">
+    <row r="42" ht="37.5" hidden="1" spans="1:16380">
       <c r="A42" s="4">
         <f>COUNTA($A$1:A41)</f>
         <v>11</v>
@@ -3146,7 +3135,7 @@
       <c r="L42" s="18"/>
       <c r="XEZ42"/>
     </row>
-    <row r="43" ht="35" spans="1:16380">
+    <row r="43" ht="37.5" hidden="1" spans="1:16380">
       <c r="A43" s="4">
         <f>COUNTA($A$1:A42)</f>
         <v>12</v>
@@ -3174,7 +3163,7 @@
       <c r="L43" s="18"/>
       <c r="XEZ43"/>
     </row>
-    <row r="44" spans="1:16380">
+    <row r="44" hidden="1" spans="1:16380">
       <c r="A44" s="4">
         <f>COUNTA($A$1:A43)</f>
         <v>13</v>
@@ -3202,7 +3191,7 @@
       <c r="L44" s="18"/>
       <c r="XEZ44"/>
     </row>
-    <row r="45" ht="52.5" spans="1:16380">
+    <row r="45" ht="56.25" spans="1:16380">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -3221,7 +3210,7 @@
       <c r="L45" s="18"/>
       <c r="XEZ45"/>
     </row>
-    <row r="46" ht="35" spans="1:16380">
+    <row r="46" ht="37.5" spans="1:16380">
       <c r="A46" s="4">
         <f>COUNTA($A$1:A45)</f>
         <v>14</v>
@@ -3249,7 +3238,7 @@
       <c r="L46" s="18"/>
       <c r="XEZ46"/>
     </row>
-    <row r="47" ht="35" spans="1:16380">
+    <row r="47" ht="37.5" spans="1:16380">
       <c r="A47" s="4">
         <f>COUNTA($A$1:A46)</f>
         <v>15</v>
@@ -3277,7 +3266,7 @@
       <c r="L47" s="18"/>
       <c r="XEZ47"/>
     </row>
-    <row r="48" ht="52.5" spans="1:16380">
+    <row r="48" ht="56.25" spans="1:16380">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -3296,7 +3285,7 @@
       <c r="L48" s="18"/>
       <c r="XEZ48"/>
     </row>
-    <row r="49" ht="35" spans="1:16380">
+    <row r="49" ht="37.5" hidden="1" spans="1:16380">
       <c r="A49" s="4">
         <f>COUNTA($A$1:A48)</f>
         <v>16</v>
@@ -3324,7 +3313,7 @@
       <c r="L49" s="18"/>
       <c r="XEZ49"/>
     </row>
-    <row r="50" ht="35" spans="1:16380">
+    <row r="50" ht="37.5" spans="1:16380">
       <c r="A50" s="4">
         <f>COUNTA($A$1:A49)</f>
         <v>17</v>
@@ -3352,7 +3341,7 @@
       <c r="L50" s="18"/>
       <c r="XEZ50"/>
     </row>
-    <row r="51" ht="35" spans="1:16380">
+    <row r="51" ht="37.5" spans="1:16380">
       <c r="A51" s="4">
         <f>COUNTA($A$1:A50)</f>
         <v>18</v>
@@ -3380,7 +3369,7 @@
       <c r="L51" s="18"/>
       <c r="XEZ51"/>
     </row>
-    <row r="52" ht="35" spans="1:16380">
+    <row r="52" ht="37.5" spans="1:16380">
       <c r="A52" s="4">
         <f>COUNTA($A$1:A51)</f>
         <v>19</v>
@@ -3408,7 +3397,7 @@
       <c r="L52" s="18"/>
       <c r="XEZ52"/>
     </row>
-    <row r="53" ht="35" spans="1:16380">
+    <row r="53" ht="37.5" hidden="1" spans="1:16380">
       <c r="A53" s="4">
         <f>COUNTA($A$1:A52)</f>
         <v>20</v>
@@ -3436,7 +3425,7 @@
       <c r="L53" s="18"/>
       <c r="XEZ53"/>
     </row>
-    <row r="54" ht="35" spans="1:16380">
+    <row r="54" ht="37.5" spans="1:16380">
       <c r="A54" s="4">
         <f>COUNTA($A$1:A53)</f>
         <v>21</v>
@@ -3464,7 +3453,7 @@
       <c r="L54" s="18"/>
       <c r="XEZ54"/>
     </row>
-    <row r="55" ht="35" spans="1:16380">
+    <row r="55" ht="37.5" hidden="1" spans="1:16380">
       <c r="A55" s="4">
         <f>COUNTA($A$1:A54)</f>
         <v>22</v>
@@ -3520,7 +3509,7 @@
       <c r="L56" s="18"/>
       <c r="XEZ56"/>
     </row>
-    <row r="57" ht="70" spans="1:16380">
+    <row r="57" ht="75" hidden="1" spans="1:16380">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3539,7 +3528,7 @@
       <c r="L57" s="18"/>
       <c r="XEZ57"/>
     </row>
-    <row r="58" ht="70" spans="1:16380">
+    <row r="58" ht="75" hidden="1" spans="1:16380">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -3605,7 +3594,7 @@
       <c r="L60" s="18"/>
       <c r="XEZ60"/>
     </row>
-    <row r="61" ht="35" spans="1:16380">
+    <row r="61" ht="37.5" spans="1:16380">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -3624,7 +3613,7 @@
       <c r="L61" s="18"/>
       <c r="XEZ61"/>
     </row>
-    <row r="62" ht="35" spans="1:16380">
+    <row r="62" ht="37.5" spans="1:16380">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -3690,7 +3679,7 @@
       <c r="L64" s="18"/>
       <c r="XEZ64"/>
     </row>
-    <row r="65" ht="35" spans="1:16380">
+    <row r="65" ht="37.5" spans="1:16380">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -3709,7 +3698,7 @@
       <c r="L65" s="18"/>
       <c r="XEZ65"/>
     </row>
-    <row r="66" ht="35" spans="1:16380">
+    <row r="66" ht="37.5" spans="1:16380">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -3775,7 +3764,7 @@
       <c r="L68" s="18"/>
       <c r="XEZ68"/>
     </row>
-    <row r="69" ht="52.5" spans="1:16380">
+    <row r="69" ht="56.25" hidden="1" spans="1:16380">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -3794,7 +3783,7 @@
       <c r="L69" s="18"/>
       <c r="XEZ69"/>
     </row>
-    <row r="70" ht="35" spans="1:16380">
+    <row r="70" ht="37.5" spans="1:16380">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -3832,7 +3821,7 @@
       <c r="L71" s="18"/>
       <c r="XEZ71"/>
     </row>
-    <row r="72" ht="35" spans="1:16380">
+    <row r="72" ht="56.25" spans="1:16380">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -3879,7 +3868,7 @@
       <c r="L73" s="18"/>
       <c r="XEZ73"/>
     </row>
-    <row r="74" ht="35" spans="1:16380">
+    <row r="74" ht="37.5" spans="1:16380">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -3898,7 +3887,7 @@
       <c r="L74" s="18"/>
       <c r="XEZ74"/>
     </row>
-    <row r="75" ht="35" spans="1:16380">
+    <row r="75" ht="37.5" spans="1:16380">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -3964,7 +3953,7 @@
       <c r="L77" s="18"/>
       <c r="XEZ77"/>
     </row>
-    <row r="78" ht="35" spans="1:16380">
+    <row r="78" ht="37.5" hidden="1" spans="1:16380">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -3983,7 +3972,7 @@
       <c r="L78" s="18"/>
       <c r="XEZ78"/>
     </row>
-    <row r="79" ht="35" spans="1:16380">
+    <row r="79" ht="37.5" hidden="1" spans="1:16380">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -4002,7 +3991,7 @@
       <c r="L79" s="18"/>
       <c r="XEZ79"/>
     </row>
-    <row r="80" ht="52.5" spans="1:16380">
+    <row r="80" ht="56.25" spans="1:16380">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -4068,7 +4057,7 @@
       <c r="L82" s="18"/>
       <c r="XEZ82"/>
     </row>
-    <row r="83" ht="35" spans="1:16380">
+    <row r="83" ht="37.5" spans="1:16380">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -4087,7 +4076,7 @@
       <c r="L83" s="18"/>
       <c r="XEZ83"/>
     </row>
-    <row r="84" ht="35" spans="1:16380">
+    <row r="84" ht="37.5" spans="1:16380">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -4153,7 +4142,7 @@
       <c r="L86" s="18"/>
       <c r="XEZ86"/>
     </row>
-    <row r="87" ht="35" spans="1:16380">
+    <row r="87" ht="37.5" spans="1:16380">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -4172,7 +4161,7 @@
       <c r="L87" s="18"/>
       <c r="XEZ87"/>
     </row>
-    <row r="88" ht="35" spans="1:16380">
+    <row r="88" ht="37.5" spans="1:16380">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -4191,7 +4180,7 @@
       <c r="L88" s="18"/>
       <c r="XEZ88"/>
     </row>
-    <row r="89" ht="52.5" spans="1:16380">
+    <row r="89" ht="56.25" spans="1:16380">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -4210,7 +4199,7 @@
       <c r="L89" s="18"/>
       <c r="XEZ89"/>
     </row>
-    <row r="90" ht="35" spans="1:16380">
+    <row r="90" ht="37.5" spans="1:16380">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -4257,7 +4246,7 @@
       <c r="L91" s="18"/>
       <c r="XEZ91"/>
     </row>
-    <row r="92" ht="35" spans="1:16380">
+    <row r="92" ht="37.5" spans="1:16380">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -4276,7 +4265,7 @@
       <c r="L92" s="18"/>
       <c r="XEZ92"/>
     </row>
-    <row r="93" ht="35" spans="1:16380">
+    <row r="93" ht="37.5" spans="1:16380">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -4314,7 +4303,7 @@
       <c r="L94" s="18"/>
       <c r="XEZ94"/>
     </row>
-    <row r="95" ht="35" spans="1:16380">
+    <row r="95" ht="56.25" spans="1:16380">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -4333,7 +4322,7 @@
       <c r="L95" s="18"/>
       <c r="XEZ95"/>
     </row>
-    <row r="96" ht="35" spans="1:16380">
+    <row r="96" ht="37.5" spans="1:16380">
       <c r="A96" s="4">
         <f>COUNTA($A$1:A94)</f>
         <v>32</v>
@@ -4361,7 +4350,7 @@
       <c r="L96" s="18"/>
       <c r="XEZ96"/>
     </row>
-    <row r="97" ht="52.5" spans="1:16380">
+    <row r="97" ht="56.25" spans="1:16380">
       <c r="A97" s="4">
         <f>COUNTA($A$1:A96)</f>
         <v>33</v>
@@ -4389,7 +4378,7 @@
       <c r="L97" s="18"/>
       <c r="XEZ97"/>
     </row>
-    <row r="98" ht="52.5" spans="1:16380">
+    <row r="98" ht="56.25" spans="1:16380">
       <c r="A98" s="4">
         <f>COUNTA($A$1:A97)</f>
         <v>34</v>
@@ -4415,7 +4404,7 @@
       <c r="L98" s="18"/>
       <c r="XEZ98"/>
     </row>
-    <row r="99" ht="35" spans="1:16380">
+    <row r="99" ht="37.5" spans="1:16380">
       <c r="A99" s="4">
         <f>COUNTA($A$1:A98)</f>
         <v>35</v>
@@ -4443,7 +4432,7 @@
       <c r="L99" s="18"/>
       <c r="XEZ99"/>
     </row>
-    <row r="100" ht="35" spans="1:16380">
+    <row r="100" ht="37.5" spans="1:16380">
       <c r="A100" s="4">
         <f>COUNTA($A$1:A99)</f>
         <v>36</v>
@@ -4469,7 +4458,7 @@
       <c r="L100" s="18"/>
       <c r="XEZ100"/>
     </row>
-    <row r="101" ht="35" spans="1:16380">
+    <row r="101" ht="37.5" spans="1:16380">
       <c r="A101" s="4">
         <f>COUNTA($A$1:A100)</f>
         <v>37</v>
@@ -4497,7 +4486,7 @@
       <c r="L101" s="18"/>
       <c r="XEZ101"/>
     </row>
-    <row r="102" ht="35" spans="1:16380">
+    <row r="102" ht="37.5" hidden="1" spans="1:16380">
       <c r="A102" s="4">
         <f>COUNTA($A$1:A101)</f>
         <v>38</v>
@@ -4525,7 +4514,7 @@
       <c r="L102" s="18"/>
       <c r="XEZ102"/>
     </row>
-    <row r="103" ht="35" spans="1:16380">
+    <row r="103" ht="37.5" spans="1:16380">
       <c r="A103" s="4">
         <f>COUNTA($A$1:A102)</f>
         <v>39</v>
@@ -4553,7 +4542,7 @@
       <c r="L103" s="18"/>
       <c r="XEZ103"/>
     </row>
-    <row r="104" ht="35" spans="1:16380">
+    <row r="104" ht="37.5" hidden="1" spans="1:16380">
       <c r="A104" s="4">
         <f>COUNTA($A$1:A103)</f>
         <v>40</v>
@@ -4579,7 +4568,7 @@
       <c r="L104" s="18"/>
       <c r="XEZ104"/>
     </row>
-    <row r="105" ht="35" spans="1:16380">
+    <row r="105" ht="37.5" hidden="1" spans="1:16380">
       <c r="A105" s="4">
         <f>COUNTA($A$1:A104)</f>
         <v>41</v>
@@ -4605,7 +4594,7 @@
       <c r="L105" s="18"/>
       <c r="XEZ105"/>
     </row>
-    <row r="106" ht="35" spans="1:16380">
+    <row r="106" ht="37.5" spans="1:16380">
       <c r="A106" s="4">
         <f>COUNTA($A$1:A105)</f>
         <v>42</v>
@@ -4657,7 +4646,7 @@
       <c r="L107" s="18"/>
       <c r="XEZ107"/>
     </row>
-    <row r="108" ht="35" spans="1:16380">
+    <row r="108" ht="37.5" hidden="1" spans="1:16380">
       <c r="A108" s="4">
         <f>COUNTA($A$1:A107)</f>
         <v>44</v>
@@ -4685,7 +4674,7 @@
       <c r="L108" s="18"/>
       <c r="XEZ108"/>
     </row>
-    <row r="109" ht="35" spans="1:16380">
+    <row r="109" ht="37.5" hidden="1" spans="1:16380">
       <c r="A109" s="4">
         <f>COUNTA($A$1:A108)</f>
         <v>45</v>
@@ -4711,7 +4700,7 @@
       <c r="L109" s="18"/>
       <c r="XEZ109"/>
     </row>
-    <row r="110" ht="35" spans="1:16380">
+    <row r="110" ht="37.5" hidden="1" spans="1:16380">
       <c r="A110" s="4">
         <f>COUNTA($A$1:A109)</f>
         <v>46</v>
@@ -4737,7 +4726,7 @@
       <c r="L110" s="18"/>
       <c r="XEZ110"/>
     </row>
-    <row r="111" ht="35" spans="1:16380">
+    <row r="111" ht="37.5" hidden="1" spans="1:16380">
       <c r="A111" s="4">
         <f>COUNTA($A$1:A110)</f>
         <v>47</v>
@@ -4763,7 +4752,7 @@
       <c r="L111" s="18"/>
       <c r="XEZ111"/>
     </row>
-    <row r="112" ht="35" spans="1:16380">
+    <row r="112" ht="37.5" hidden="1" spans="1:16380">
       <c r="A112" s="4">
         <f>COUNTA($A$1:A111)</f>
         <v>48</v>
@@ -4789,7 +4778,7 @@
       <c r="L112" s="18"/>
       <c r="XEZ112"/>
     </row>
-    <row r="113" ht="35" spans="1:16380">
+    <row r="113" ht="37.5" hidden="1" spans="1:16380">
       <c r="A113" s="4">
         <f>COUNTA($A$1:A112)</f>
         <v>49</v>
@@ -4815,7 +4804,7 @@
       <c r="L113" s="18"/>
       <c r="XEZ113"/>
     </row>
-    <row r="114" ht="35" spans="1:16380">
+    <row r="114" ht="37.5" hidden="1" spans="1:16380">
       <c r="A114" s="4">
         <f>COUNTA($A$1:A113)</f>
         <v>50</v>
@@ -4841,7 +4830,7 @@
       <c r="L114" s="18"/>
       <c r="XEZ114"/>
     </row>
-    <row r="115" ht="35" spans="1:16380">
+    <row r="115" ht="37.5" hidden="1" spans="1:16380">
       <c r="A115" s="4">
         <f>COUNTA($A$1:A114)</f>
         <v>51</v>
@@ -4867,7 +4856,7 @@
       <c r="L115" s="18"/>
       <c r="XEZ115"/>
     </row>
-    <row r="116" ht="35" spans="1:16380">
+    <row r="116" ht="37.5" hidden="1" spans="1:16380">
       <c r="A116" s="4">
         <f>COUNTA($A$1:A115)</f>
         <v>52</v>
@@ -4893,7 +4882,7 @@
       <c r="L116" s="18"/>
       <c r="XEZ116"/>
     </row>
-    <row r="117" ht="35" spans="1:16380">
+    <row r="117" ht="37.5" hidden="1" spans="1:16380">
       <c r="A117" s="4">
         <f>COUNTA($A$1:A116)</f>
         <v>53</v>
@@ -4919,7 +4908,7 @@
       <c r="L117" s="18"/>
       <c r="XEZ117"/>
     </row>
-    <row r="118" ht="35" spans="1:16380">
+    <row r="118" ht="37.5" hidden="1" spans="1:16380">
       <c r="A118" s="4">
         <f>COUNTA($A$1:A117)</f>
         <v>54</v>
@@ -4945,7 +4934,7 @@
       <c r="L118" s="18"/>
       <c r="XEZ118"/>
     </row>
-    <row r="119" ht="35" spans="1:16380">
+    <row r="119" ht="37.5" hidden="1" spans="1:16380">
       <c r="A119" s="4">
         <f>COUNTA($A$1:A118)</f>
         <v>55</v>
@@ -4971,7 +4960,7 @@
       <c r="L119" s="18"/>
       <c r="XEZ119"/>
     </row>
-    <row r="120" ht="35" spans="1:16380">
+    <row r="120" ht="37.5" hidden="1" spans="1:16380">
       <c r="A120" s="4">
         <f>COUNTA($A$1:A119)</f>
         <v>56</v>
@@ -4999,7 +4988,7 @@
       <c r="L120" s="18"/>
       <c r="XEZ120"/>
     </row>
-    <row r="121" ht="35" spans="1:16380">
+    <row r="121" ht="37.5" hidden="1" spans="1:16380">
       <c r="A121" s="4">
         <f>COUNTA($A$1:A120)</f>
         <v>57</v>
@@ -5027,7 +5016,7 @@
       <c r="L121" s="18"/>
       <c r="XEZ121"/>
     </row>
-    <row r="122" ht="35" spans="1:16380">
+    <row r="122" ht="37.5" spans="1:16380">
       <c r="A122" s="4">
         <f>COUNTA($A$1:A121)</f>
         <v>58</v>
@@ -5055,7 +5044,7 @@
       <c r="L122" s="18"/>
       <c r="XEZ122"/>
     </row>
-    <row r="123" ht="35" spans="1:16380">
+    <row r="123" ht="37.5" hidden="1" spans="1:16380">
       <c r="A123" s="4">
         <f>COUNTA($A$1:A122)</f>
         <v>59</v>
@@ -5083,7 +5072,7 @@
       <c r="L123" s="18"/>
       <c r="XEZ123"/>
     </row>
-    <row r="124" ht="35" spans="1:16380">
+    <row r="124" ht="37.5" spans="1:16380">
       <c r="A124" s="4">
         <f>COUNTA($A$1:A123)</f>
         <v>60</v>
@@ -5111,7 +5100,7 @@
       <c r="L124" s="18"/>
       <c r="XEZ124"/>
     </row>
-    <row r="125" ht="35" spans="1:16380">
+    <row r="125" ht="37.5" spans="1:16380">
       <c r="A125" s="4">
         <f>COUNTA($A$1:A124)</f>
         <v>61</v>
@@ -5139,7 +5128,7 @@
       <c r="L125" s="18"/>
       <c r="XEZ125"/>
     </row>
-    <row r="126" ht="35" spans="1:16380">
+    <row r="126" ht="37.5" spans="1:16380">
       <c r="A126" s="4">
         <f>COUNTA($A$1:A125)</f>
         <v>62</v>
@@ -5167,7 +5156,7 @@
       <c r="L126" s="18"/>
       <c r="XEZ126"/>
     </row>
-    <row r="127" ht="35" spans="1:16380">
+    <row r="127" ht="37.5" hidden="1" spans="1:16380">
       <c r="A127" s="4">
         <f>COUNTA($A$1:A126)</f>
         <v>63</v>
@@ -5195,7 +5184,7 @@
       <c r="L127" s="18"/>
       <c r="XEZ127"/>
     </row>
-    <row r="128" ht="35" spans="1:16380">
+    <row r="128" ht="37.5" spans="1:16380">
       <c r="A128" s="4">
         <f>COUNTA($A$1:A127)</f>
         <v>64</v>
@@ -5223,7 +5212,7 @@
       <c r="L128" s="18"/>
       <c r="XEZ128"/>
     </row>
-    <row r="129" ht="35" spans="1:16380">
+    <row r="129" ht="56.25" spans="1:16380">
       <c r="A129" s="4">
         <f>COUNTA($A$1:A128)</f>
         <v>65</v>
@@ -5251,7 +5240,7 @@
       <c r="L129" s="18"/>
       <c r="XEZ129"/>
     </row>
-    <row r="130" ht="35" spans="1:16380">
+    <row r="130" ht="37.5" hidden="1" spans="1:16380">
       <c r="A130" s="4">
         <f>COUNTA($A$1:A129)</f>
         <v>66</v>
@@ -5279,7 +5268,7 @@
       <c r="L130" s="18"/>
       <c r="XEZ130"/>
     </row>
-    <row r="131" ht="35" spans="1:16380">
+    <row r="131" ht="37.5" hidden="1" spans="1:16380">
       <c r="A131" s="4">
         <f>COUNTA($A$1:A130)</f>
         <v>67</v>
@@ -5307,7 +5296,7 @@
       <c r="L131" s="18"/>
       <c r="XEZ131"/>
     </row>
-    <row r="132" ht="35" spans="1:16380">
+    <row r="132" ht="37.5" hidden="1" spans="1:16380">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -5326,7 +5315,7 @@
       <c r="L132" s="18"/>
       <c r="XEZ132"/>
     </row>
-    <row r="133" ht="52.5" spans="1:16380">
+    <row r="133" ht="56.25" spans="1:16380">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -5345,7 +5334,7 @@
       <c r="L133" s="18"/>
       <c r="XEZ133"/>
     </row>
-    <row r="134" ht="35" spans="1:16380">
+    <row r="134" ht="37.5" hidden="1" spans="1:16380">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -5364,7 +5353,7 @@
       <c r="L134" s="18"/>
       <c r="XEZ134"/>
     </row>
-    <row r="135" ht="35" spans="1:16380">
+    <row r="135" ht="37.5" hidden="1" spans="1:16380">
       <c r="A135" s="4">
         <f>COUNTA($A$1:A134)</f>
         <v>68</v>
@@ -5392,7 +5381,7 @@
       <c r="L135" s="18"/>
       <c r="XEZ135"/>
     </row>
-    <row r="136" ht="35" spans="1:16380">
+    <row r="136" ht="37.5" hidden="1" spans="1:16380">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -5411,7 +5400,7 @@
       <c r="L136" s="18"/>
       <c r="XEZ136"/>
     </row>
-    <row r="137" ht="52.5" spans="1:16380">
+    <row r="137" ht="56.25" spans="1:16380">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -5430,7 +5419,7 @@
       <c r="L137" s="18"/>
       <c r="XEZ137"/>
     </row>
-    <row r="138" ht="35" spans="1:16380">
+    <row r="138" ht="37.5" hidden="1" spans="1:16380">
       <c r="A138" s="4"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5449,7 +5438,7 @@
       <c r="L138" s="18"/>
       <c r="XEZ138"/>
     </row>
-    <row r="139" ht="35" spans="1:16380">
+    <row r="139" ht="37.5" hidden="1" spans="1:16380">
       <c r="A139" s="4">
         <f>COUNTA($A$1:A138)</f>
         <v>69</v>
@@ -5477,7 +5466,7 @@
       <c r="L139" s="18"/>
       <c r="XEZ139"/>
     </row>
-    <row r="140" ht="35" spans="1:16380">
+    <row r="140" ht="37.5" hidden="1" spans="1:16380">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -5496,7 +5485,7 @@
       <c r="L140" s="18"/>
       <c r="XEZ140"/>
     </row>
-    <row r="141" ht="52.5" spans="1:16380">
+    <row r="141" ht="56.25" hidden="1" spans="1:16380">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -5515,7 +5504,7 @@
       <c r="L141" s="18"/>
       <c r="XEZ141"/>
     </row>
-    <row r="142" ht="35" spans="1:16380">
+    <row r="142" ht="37.5" hidden="1" spans="1:16380">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -5534,7 +5523,7 @@
       <c r="L142" s="18"/>
       <c r="XEZ142"/>
     </row>
-    <row r="143" ht="35" spans="1:16380">
+    <row r="143" ht="37.5" hidden="1" spans="1:16380">
       <c r="A143" s="4">
         <f>COUNTA($A$1:A142)</f>
         <v>70</v>
@@ -5562,7 +5551,7 @@
       <c r="L143" s="18"/>
       <c r="XEZ143"/>
     </row>
-    <row r="144" ht="35" spans="1:16380">
+    <row r="144" ht="37.5" hidden="1" spans="1:16380">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -5581,7 +5570,7 @@
       <c r="L144" s="18"/>
       <c r="XEZ144"/>
     </row>
-    <row r="145" ht="52.5" spans="1:16380">
+    <row r="145" ht="56.25" hidden="1" spans="1:16380">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -5600,7 +5589,7 @@
       <c r="L145" s="18"/>
       <c r="XEZ145"/>
     </row>
-    <row r="146" ht="35" spans="1:16380">
+    <row r="146" ht="37.5" hidden="1" spans="1:16380">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -5619,7 +5608,7 @@
       <c r="L146" s="18"/>
       <c r="XEZ146"/>
     </row>
-    <row r="147" ht="35" spans="1:16380">
+    <row r="147" ht="37.5" hidden="1" spans="1:16380">
       <c r="A147" s="4">
         <f>COUNTA($A$1:A146)</f>
         <v>71</v>
@@ -5647,7 +5636,7 @@
       <c r="L147" s="18"/>
       <c r="XEZ147"/>
     </row>
-    <row r="148" ht="35" spans="1:16380">
+    <row r="148" ht="37.5" hidden="1" spans="1:16380">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -5666,7 +5655,7 @@
       <c r="L148" s="18"/>
       <c r="XEZ148"/>
     </row>
-    <row r="149" ht="52.5" spans="1:16380">
+    <row r="149" ht="56.25" spans="1:16380">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -5685,7 +5674,7 @@
       <c r="L149" s="18"/>
       <c r="XEZ149"/>
     </row>
-    <row r="150" ht="35" spans="1:16380">
+    <row r="150" ht="37.5" hidden="1" spans="1:16380">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -5704,7 +5693,7 @@
       <c r="L150" s="18"/>
       <c r="XEZ150"/>
     </row>
-    <row r="151" ht="35" spans="1:16380">
+    <row r="151" ht="37.5" hidden="1" spans="1:16380">
       <c r="A151" s="4">
         <f>COUNTA($A$1:A150)</f>
         <v>72</v>
@@ -5732,7 +5721,7 @@
       <c r="L151" s="18"/>
       <c r="XEZ151"/>
     </row>
-    <row r="152" ht="35" spans="1:16380">
+    <row r="152" ht="37.5" hidden="1" spans="1:16380">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -5751,7 +5740,7 @@
       <c r="L152" s="18"/>
       <c r="XEZ152"/>
     </row>
-    <row r="153" ht="52.5" spans="1:16380">
+    <row r="153" ht="56.25" spans="1:16380">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -5770,7 +5759,7 @@
       <c r="L153" s="18"/>
       <c r="XEZ153"/>
     </row>
-    <row r="154" ht="35" spans="1:16380">
+    <row r="154" ht="37.5" hidden="1" spans="1:16380">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -5789,7 +5778,7 @@
       <c r="L154" s="18"/>
       <c r="XEZ154"/>
     </row>
-    <row r="155" ht="35" spans="1:16380">
+    <row r="155" ht="37.5" hidden="1" spans="1:16380">
       <c r="A155" s="4">
         <f>COUNTA($A$1:A154)</f>
         <v>73</v>
@@ -5817,7 +5806,7 @@
       <c r="L155" s="18"/>
       <c r="XEZ155"/>
     </row>
-    <row r="156" ht="35" spans="1:16380">
+    <row r="156" ht="37.5" hidden="1" spans="1:16380">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -5836,7 +5825,7 @@
       <c r="L156" s="18"/>
       <c r="XEZ156"/>
     </row>
-    <row r="157" ht="52.5" spans="1:16380">
+    <row r="157" ht="56.25" spans="1:16380">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -5855,7 +5844,7 @@
       <c r="L157" s="18"/>
       <c r="XEZ157"/>
     </row>
-    <row r="158" ht="35" spans="1:16380">
+    <row r="158" ht="37.5" hidden="1" spans="1:16380">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -5874,7 +5863,7 @@
       <c r="L158" s="18"/>
       <c r="XEZ158"/>
     </row>
-    <row r="159" ht="35" spans="1:16380">
+    <row r="159" ht="37.5" hidden="1" spans="1:16380">
       <c r="A159" s="4">
         <f>COUNTA($A$1:A158)</f>
         <v>74</v>
@@ -5902,7 +5891,7 @@
       <c r="L159" s="18"/>
       <c r="XEZ159"/>
     </row>
-    <row r="160" ht="35" spans="1:16380">
+    <row r="160" ht="37.5" hidden="1" spans="1:16380">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -5921,7 +5910,7 @@
       <c r="L160" s="18"/>
       <c r="XEZ160"/>
     </row>
-    <row r="161" ht="52.5" spans="1:16380">
+    <row r="161" ht="56.25" spans="1:16380">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -5940,7 +5929,7 @@
       <c r="L161" s="18"/>
       <c r="XEZ161"/>
     </row>
-    <row r="162" ht="35" spans="1:16380">
+    <row r="162" ht="37.5" hidden="1" spans="1:16380">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -5959,7 +5948,7 @@
       <c r="L162" s="18"/>
       <c r="XEZ162"/>
     </row>
-    <row r="163" ht="35" spans="1:16380">
+    <row r="163" ht="37.5" spans="1:16380">
       <c r="A163" s="4">
         <f>COUNTA($A$1:A162)</f>
         <v>75</v>
@@ -5987,7 +5976,7 @@
       <c r="L163" s="18"/>
       <c r="XEZ163"/>
     </row>
-    <row r="164" ht="35" spans="1:16380">
+    <row r="164" ht="37.5" spans="1:16380">
       <c r="A164" s="4">
         <f>COUNTA($A$1:A163)</f>
         <v>76</v>
@@ -6015,7 +6004,7 @@
       <c r="L164" s="18"/>
       <c r="XEZ164"/>
     </row>
-    <row r="165" ht="52.5" spans="1:16380">
+    <row r="165" ht="56.25" spans="1:16380">
       <c r="A165" s="4">
         <f>COUNTA($A$1:A164)</f>
         <v>77</v>
@@ -6043,7 +6032,7 @@
       <c r="L165" s="18"/>
       <c r="XEZ165"/>
     </row>
-    <row r="166" ht="35" spans="1:16380">
+    <row r="166" ht="37.5" spans="1:16380">
       <c r="A166" s="4">
         <f>COUNTA($A$1:A165)</f>
         <v>78</v>
@@ -6071,7 +6060,7 @@
       <c r="L166" s="18"/>
       <c r="XEZ166"/>
     </row>
-    <row r="167" ht="35" spans="1:16380">
+    <row r="167" ht="37.5" spans="1:16380">
       <c r="A167" s="4">
         <f>COUNTA($A$1:A166)</f>
         <v>79</v>
@@ -6099,7 +6088,7 @@
       <c r="L167" s="18"/>
       <c r="XEZ167"/>
     </row>
-    <row r="168" ht="35" spans="1:16380">
+    <row r="168" ht="37.5" spans="1:16380">
       <c r="A168" s="4">
         <f>COUNTA($A$1:A167)</f>
         <v>80</v>
@@ -6127,7 +6116,7 @@
       <c r="L168" s="18"/>
       <c r="XEZ168"/>
     </row>
-    <row r="169" ht="35" spans="1:16380">
+    <row r="169" ht="37.5" spans="1:16380">
       <c r="A169" s="4">
         <f>COUNTA($A$1:A168)</f>
         <v>81</v>
@@ -6155,7 +6144,7 @@
       <c r="L169" s="18"/>
       <c r="XEZ169"/>
     </row>
-    <row r="170" ht="35" spans="1:16380">
+    <row r="170" ht="56.25" hidden="1" spans="1:16380">
       <c r="A170" s="4">
         <f>COUNTA($A$1:A169)</f>
         <v>82</v>
@@ -6183,7 +6172,7 @@
       <c r="L170" s="18"/>
       <c r="XEZ170"/>
     </row>
-    <row r="171" ht="52.5" spans="1:16380">
+    <row r="171" ht="56.25" spans="1:16380">
       <c r="A171" s="4">
         <f>COUNTA($A$1:A170)</f>
         <v>83</v>
@@ -6211,7 +6200,7 @@
       <c r="L171" s="18"/>
       <c r="XEZ171"/>
     </row>
-    <row r="172" ht="35" spans="1:16380">
+    <row r="172" ht="56.25" spans="1:16380">
       <c r="A172" s="4">
         <f>COUNTA($A$1:A171)</f>
         <v>84</v>
@@ -6239,7 +6228,7 @@
       <c r="L172" s="18"/>
       <c r="XEZ172"/>
     </row>
-    <row r="173" ht="35" spans="1:16380">
+    <row r="173" ht="56.25" spans="1:16380">
       <c r="A173" s="4">
         <f>COUNTA($A$1:A172)</f>
         <v>85</v>
@@ -6336,7 +6325,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="178" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="178" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A178" s="4">
         <f>COUNTA($A$1:A177)</f>
         <v>87</v>
@@ -6360,7 +6349,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="179" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="179" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A179" s="4"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -6371,7 +6360,7 @@
       <c r="F179" s="7"/>
       <c r="G179" s="32"/>
     </row>
-    <row r="180" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="180" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A180" s="4"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -6382,7 +6371,7 @@
       <c r="F180" s="7"/>
       <c r="G180" s="32"/>
     </row>
-    <row r="181" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="181" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A181" s="4"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -6393,7 +6382,7 @@
       <c r="F181" s="7"/>
       <c r="G181" s="32"/>
     </row>
-    <row r="182" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="182" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A182" s="4">
         <f>COUNTA($A$1:A181)</f>
         <v>88</v>
@@ -6417,7 +6406,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="183" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="183" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A183" s="4"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -6428,7 +6417,7 @@
       <c r="F183" s="7"/>
       <c r="G183" s="32"/>
     </row>
-    <row r="184" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="184" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A184" s="4"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -6439,7 +6428,7 @@
       <c r="F184" s="7"/>
       <c r="G184" s="32"/>
     </row>
-    <row r="185" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="185" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A185" s="4"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -6726,7 +6715,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="202" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="202" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A202" s="4">
         <f>COUNTA($A$1:A201)</f>
         <v>93</v>
@@ -6750,7 +6739,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="203" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="203" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A203" s="4"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -6765,7 +6754,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="204" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="204" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A204" s="4"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -6780,7 +6769,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="205" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="205" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A205" s="4"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -6888,7 +6877,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="211" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="211" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A211" s="4"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -7026,7 +7015,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="219" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="219" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A219" s="4"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -7041,7 +7030,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="220" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="220" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A220" s="4"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -7056,7 +7045,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="221" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="221" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A221" s="4"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -7071,7 +7060,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="222" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="222" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A222" s="4">
         <f>COUNTA($A$1:A221)</f>
         <v>98</v>
@@ -7095,7 +7084,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="223" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="223" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A223" s="4"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -7110,7 +7099,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="224" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="224" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A224" s="4"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -7125,7 +7114,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="225" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="225" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A225" s="4"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -7140,7 +7129,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="226" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="226" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A226" s="4">
         <f>COUNTA($A$1:A225)</f>
         <v>99</v>
@@ -7164,7 +7153,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="227" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="227" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A227" s="4"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -7179,7 +7168,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="228" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="228" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A228" s="4"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -7194,7 +7183,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="229" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="229" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A229" s="4"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -7209,7 +7198,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="230" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="230" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A230" s="4">
         <f>COUNTA($A$1:A229)</f>
         <v>100</v>
@@ -7233,7 +7222,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="231" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="231" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A231" s="4"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -7248,7 +7237,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="232" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="232" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A232" s="4"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -7263,7 +7252,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="233" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="233" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A233" s="4"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -7278,7 +7267,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="234" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="234" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A234" s="4">
         <f>COUNTA($A$1:A233)</f>
         <v>101</v>
@@ -7302,7 +7291,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="235" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="235" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A235" s="4"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -7317,7 +7306,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="236" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="236" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A236" s="4"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -7332,7 +7321,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="237" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="237" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A237" s="4"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -7347,7 +7336,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="238" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="238" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A238" s="4">
         <f>COUNTA($A$1:A237)</f>
         <v>102</v>
@@ -7371,7 +7360,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="239" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="239" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A239" s="4"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -7386,7 +7375,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="240" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="240" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A240" s="4"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -7401,7 +7390,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="241" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="241" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A241" s="4"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -7440,7 +7429,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="243" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="243" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A243" s="4"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -7509,7 +7498,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="247" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="247" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A247" s="4"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -7524,7 +7513,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="248" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="248" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A248" s="4"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -7539,7 +7528,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="249" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="249" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A249" s="4"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -7662,7 +7651,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="256" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="256" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A256" s="4"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -7998,7 +7987,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="276" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="276" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A276" s="4"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -8013,7 +8002,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="277" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="277" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A277" s="4"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -8043,7 +8032,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="279" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="279" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A279" s="4"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -8166,7 +8155,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="286" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="286" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A286" s="4"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -8181,7 +8170,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="287" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="287" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A287" s="4"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -8586,7 +8575,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="311" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="311" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A311" s="4"/>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
@@ -8601,7 +8590,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="312" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="312" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A312" s="4"/>
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
@@ -8616,7 +8605,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="313" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="313" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A313" s="4"/>
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
@@ -8715,7 +8704,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="319" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="319" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A319" s="4">
         <f>COUNTA($A$1:A318)</f>
         <v>119</v>
@@ -8739,7 +8728,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="320" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="320" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A320" s="4"/>
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
@@ -8754,7 +8743,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="321" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="321" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A321" s="4"/>
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
@@ -8769,7 +8758,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="322" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="322" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A322" s="4"/>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
@@ -8784,7 +8773,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="323" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="323" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A323" s="4"/>
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
@@ -9219,7 +9208,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="349" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="349" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A349" s="4">
         <f>COUNTA($A$1:A348)</f>
         <v>125</v>
@@ -10113,7 +10102,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="402" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="402" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A402" s="4"/>
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
@@ -10212,7 +10201,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="408" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="408" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A408" s="4">
         <f>COUNTA($A$1:A407)</f>
         <v>137</v>
@@ -10236,7 +10225,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="409" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="409" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A409" s="4"/>
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
@@ -10251,7 +10240,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="410" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="410" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A410" s="4"/>
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
@@ -10281,7 +10270,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="412" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="412" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A412" s="4"/>
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
@@ -10296,7 +10285,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="413" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="413" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A413" s="4">
         <f>COUNTA($A$1:A412)</f>
         <v>138</v>
@@ -10320,7 +10309,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="414" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="414" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A414" s="4"/>
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
@@ -10335,7 +10324,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="415" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="415" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A415" s="4"/>
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
@@ -10350,7 +10339,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="416" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="416" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A416" s="4"/>
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
@@ -10365,7 +10354,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="417" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="417" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A417" s="4"/>
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
@@ -10488,7 +10477,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="424" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="424" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A424" s="4"/>
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
@@ -10968,7 +10957,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="453" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="453" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A453" s="4">
         <f>COUNTA($A$1:A452)</f>
         <v>146</v>
@@ -10992,7 +10981,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="454" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="454" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A454" s="4"/>
       <c r="B454" s="5"/>
       <c r="C454" s="5"/>
@@ -11007,7 +10996,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="455" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="455" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A455" s="4"/>
       <c r="B455" s="5"/>
       <c r="C455" s="5"/>
@@ -11037,7 +11026,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="457" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="457" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A457" s="4"/>
       <c r="B457" s="5"/>
       <c r="C457" s="5"/>
@@ -11220,7 +11209,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="468" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="468" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A468" s="4">
         <f>COUNTA($A$1:A467)</f>
         <v>149</v>
@@ -11244,7 +11233,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="469" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="469" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A469" s="4"/>
       <c r="B469" s="5"/>
       <c r="C469" s="5"/>
@@ -11255,7 +11244,7 @@
       <c r="F469" s="7"/>
       <c r="G469" s="32"/>
     </row>
-    <row r="470" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="470" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A470" s="4"/>
       <c r="B470" s="5"/>
       <c r="C470" s="5"/>
@@ -11266,7 +11255,7 @@
       <c r="F470" s="7"/>
       <c r="G470" s="32"/>
     </row>
-    <row r="471" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="471" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A471" s="4"/>
       <c r="B471" s="5"/>
       <c r="C471" s="5"/>
@@ -11469,7 +11458,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="483" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="483" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A483" s="4"/>
       <c r="B483" s="5"/>
       <c r="C483" s="5"/>
@@ -11697,7 +11686,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="497" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="497" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A497" s="4">
         <f>COUNTA($A$1:A496)</f>
         <v>155</v>
@@ -11721,7 +11710,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="498" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="498" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A498" s="4"/>
       <c r="B498" s="5"/>
       <c r="C498" s="5"/>
@@ -11732,7 +11721,7 @@
       <c r="F498" s="7"/>
       <c r="G498" s="32"/>
     </row>
-    <row r="499" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="499" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A499" s="4"/>
       <c r="B499" s="5"/>
       <c r="C499" s="5"/>
@@ -11743,7 +11732,7 @@
       <c r="F499" s="7"/>
       <c r="G499" s="32"/>
     </row>
-    <row r="500" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="500" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A500" s="4"/>
       <c r="B500" s="5"/>
       <c r="C500" s="5"/>
@@ -11922,7 +11911,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="511" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="511" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A511" s="4">
         <f>COUNTA($A$1:A510)</f>
         <v>158</v>
@@ -11946,7 +11935,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="512" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="512" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A512" s="4"/>
       <c r="B512" s="5"/>
       <c r="C512" s="5"/>
@@ -11957,7 +11946,7 @@
       <c r="F512" s="7"/>
       <c r="G512" s="32"/>
     </row>
-    <row r="513" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="513" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A513" s="4"/>
       <c r="B513" s="5"/>
       <c r="C513" s="5"/>
@@ -11968,7 +11957,7 @@
       <c r="F513" s="7"/>
       <c r="G513" s="32"/>
     </row>
-    <row r="514" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="514" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A514" s="4"/>
       <c r="B514" s="5"/>
       <c r="C514" s="5"/>
@@ -12255,7 +12244,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="531" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="531" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A531" s="4"/>
       <c r="B531" s="5"/>
       <c r="C531" s="5"/>
@@ -12270,7 +12259,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="532" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="532" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A532" s="4"/>
       <c r="B532" s="5"/>
       <c r="C532" s="5"/>
@@ -12453,7 +12442,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="543" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="543" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A543" s="4">
         <f>COUNTA($A$1:A542)</f>
         <v>165</v>
@@ -12477,7 +12466,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="544" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="544" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A544" s="4"/>
       <c r="B544" s="5"/>
       <c r="C544" s="5"/>
@@ -12488,7 +12477,7 @@
       <c r="F544" s="7"/>
       <c r="G544" s="32"/>
     </row>
-    <row r="545" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="545" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A545" s="4"/>
       <c r="B545" s="5"/>
       <c r="C545" s="5"/>
@@ -12499,7 +12488,7 @@
       <c r="F545" s="7"/>
       <c r="G545" s="32"/>
     </row>
-    <row r="546" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="546" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A546" s="4"/>
       <c r="B546" s="5"/>
       <c r="C546" s="5"/>
@@ -12510,7 +12499,7 @@
       <c r="F546" s="7"/>
       <c r="G546" s="32"/>
     </row>
-    <row r="547" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="547" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A547" s="4"/>
       <c r="B547" s="5"/>
       <c r="C547" s="5"/>
@@ -13568,7 +13557,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="610" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="610" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A610" s="4">
         <f>COUNTA($A$1:A609)</f>
         <v>179</v>
@@ -13592,7 +13581,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="611" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="611" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A611" s="4"/>
       <c r="B611" s="5"/>
       <c r="C611" s="5"/>
@@ -13603,7 +13592,7 @@
       <c r="F611" s="7"/>
       <c r="G611" s="32"/>
     </row>
-    <row r="612" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="612" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A612" s="4"/>
       <c r="B612" s="5"/>
       <c r="C612" s="5"/>
@@ -13614,7 +13603,7 @@
       <c r="F612" s="7"/>
       <c r="G612" s="32"/>
     </row>
-    <row r="613" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="613" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A613" s="4"/>
       <c r="B613" s="5"/>
       <c r="C613" s="5"/>
@@ -13733,7 +13722,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="620" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="620" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A620" s="4"/>
       <c r="B620" s="5"/>
       <c r="C620" s="5"/>
@@ -13862,7 +13851,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="628" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="628" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A628" s="4">
         <f>COUNTA($A$1:A627)</f>
         <v>183</v>
@@ -13886,7 +13875,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="629" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="629" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A629" s="4"/>
       <c r="B629" s="5"/>
       <c r="C629" s="5"/>
@@ -13897,7 +13886,7 @@
       <c r="F629" s="7"/>
       <c r="G629" s="32"/>
     </row>
-    <row r="630" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="630" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A630" s="4"/>
       <c r="B630" s="5"/>
       <c r="C630" s="5"/>
@@ -13908,7 +13897,7 @@
       <c r="F630" s="7"/>
       <c r="G630" s="32"/>
     </row>
-    <row r="631" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="631" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A631" s="4"/>
       <c r="B631" s="5"/>
       <c r="C631" s="5"/>
@@ -14003,7 +13992,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="637" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="637" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A637" s="4">
         <f>COUNTA($A$1:A635)</f>
         <v>185</v>
@@ -14027,7 +14016,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="638" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="638" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A638" s="4"/>
       <c r="B638" s="5"/>
       <c r="C638" s="5"/>
@@ -14038,7 +14027,7 @@
       <c r="F638" s="7"/>
       <c r="G638" s="32"/>
     </row>
-    <row r="639" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="639" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A639" s="4"/>
       <c r="B639" s="5"/>
       <c r="C639" s="5"/>
@@ -14049,7 +14038,7 @@
       <c r="F639" s="7"/>
       <c r="G639" s="32"/>
     </row>
-    <row r="640" s="17" customFormat="1" ht="44.1" customHeight="1" spans="1:7">
+    <row r="640" s="17" customFormat="1" ht="44.1" hidden="1" customHeight="1" spans="1:7">
       <c r="A640" s="4"/>
       <c r="B640" s="5"/>
       <c r="C640" s="5"/>
@@ -14061,6 +14050,14 @@
       <c r="G640" s="32"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="F1:F640" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="是"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <mergeCells count="530">
     <mergeCell ref="A2:A8"/>
     <mergeCell ref="A9:A15"/>
@@ -14605,7 +14602,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="7" style="10" customWidth="1"/>
     <col min="2" max="2" width="15.875" style="10" customWidth="1"/>
@@ -14615,7 +14612,7 @@
     <col min="7" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.5" spans="1:6">
+    <row r="1" ht="18.75" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -14635,7 +14632,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="2" ht="35" spans="1:6">
+    <row r="2" ht="37.5" spans="1:6">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -14655,7 +14652,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="3" ht="35" spans="1:6">
+    <row r="3" ht="37.5" spans="1:6">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -14675,7 +14672,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="4" ht="35" spans="1:6">
+    <row r="4" ht="37.5" spans="1:6">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -14693,7 +14690,7 @@
       </c>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" ht="35" spans="1:6">
+    <row r="5" ht="37.5" spans="1:6">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -14711,7 +14708,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" ht="17.5" spans="1:6">
+    <row r="6" ht="18.75" spans="1:6">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -14729,7 +14726,7 @@
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" ht="35" spans="1:6">
+    <row r="7" ht="37.5" spans="1:6">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -14747,7 +14744,7 @@
       </c>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" ht="17.5" spans="1:6">
+    <row r="8" ht="18.75" spans="1:6">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -14765,7 +14762,7 @@
       </c>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" ht="17.5" spans="1:6">
+    <row r="9" ht="18.75" spans="1:6">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -14783,7 +14780,7 @@
       </c>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" ht="35" spans="1:6">
+    <row r="10" ht="37.5" spans="1:6">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -14801,7 +14798,7 @@
       </c>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" ht="17.5" spans="1:6">
+    <row r="11" ht="18.75" spans="1:6">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -14819,7 +14816,7 @@
       </c>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" ht="35" spans="1:6">
+    <row r="12" ht="37.5" spans="1:6">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -14837,7 +14834,7 @@
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" ht="17.5" spans="1:6">
+    <row r="13" ht="18.75" spans="1:6">
       <c r="A13" s="13" t="s">
         <v>285</v>
       </c>
@@ -14867,7 +14864,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F1048558"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="17.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.5" style="3" customWidth="1"/>
@@ -14877,7 +14874,7 @@
     <col min="6" max="6" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" spans="1:6">
+    <row r="1" ht="37.5" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -14897,7 +14894,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="2" ht="70" spans="1:6">
+    <row r="2" ht="75" spans="1:6">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -14917,7 +14914,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" ht="70" spans="1:6">
+    <row r="3" ht="71.25" spans="1:6">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -14937,7 +14934,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="4" ht="70" spans="1:6">
+    <row r="4" ht="71.25" spans="1:6">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -14957,7 +14954,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="5" ht="35" spans="1:6">
+    <row r="5" ht="37.5" spans="1:6">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -14977,7 +14974,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" ht="70" spans="1:6">
+    <row r="6" ht="75" spans="1:6">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -14997,7 +14994,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" ht="70" spans="1:6">
+    <row r="7" ht="75" spans="1:6">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -15017,7 +15014,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" ht="70" spans="1:6">
+    <row r="8" ht="71.25" spans="1:6">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -15029,7 +15026,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="9" ht="35" spans="1:6">
+    <row r="9" ht="37.5" spans="1:6">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -15069,7 +15066,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" ht="70" spans="1:6">
+    <row r="11" ht="71.25" spans="1:6">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -15081,7 +15078,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="12" ht="35" spans="1:6">
+    <row r="12" ht="37.5" spans="1:6">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -15122,7 +15119,7 @@
       <c r="D15" s="8"/>
       <c r="F15" s="9"/>
     </row>
-    <row r="17" ht="35" spans="1:6">
+    <row r="17" ht="37.5" spans="1:6">
       <c r="A17" s="2" t="s">
         <v>0</v>
       </c>
@@ -15142,7 +15139,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="18" ht="35" spans="1:6">
+    <row r="18" ht="37.5" spans="1:6">
       <c r="A18" s="5">
         <v>1</v>
       </c>
@@ -15162,7 +15159,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" ht="35" spans="1:6">
+    <row r="19" ht="37.5" spans="1:6">
       <c r="A19" s="5">
         <v>2</v>
       </c>
@@ -15182,7 +15179,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" ht="35" spans="1:6">
+    <row r="20" ht="37.5" spans="1:6">
       <c r="A20" s="5">
         <v>3</v>
       </c>
@@ -15202,7 +15199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" ht="35" spans="1:6">
+    <row r="21" ht="37.5" spans="1:6">
       <c r="A21" s="5">
         <v>4</v>
       </c>
@@ -15222,7 +15219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" ht="35" spans="1:6">
+    <row r="22" ht="37.5" spans="1:6">
       <c r="A22" s="5">
         <v>5</v>
       </c>
@@ -15242,7 +15239,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" ht="70" spans="1:6">
+    <row r="23" ht="71.25" spans="1:6">
       <c r="A23" s="5">
         <v>6</v>
       </c>
@@ -15262,7 +15259,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="24" ht="35" spans="1:6">
+    <row r="24" ht="37.5" spans="1:6">
       <c r="A24" s="5">
         <v>7</v>
       </c>
@@ -15282,7 +15279,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" ht="56" spans="1:6">
+    <row r="25" ht="57" spans="1:6">
       <c r="A25" s="5">
         <v>8</v>
       </c>
@@ -15302,7 +15299,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" ht="35" spans="1:6">
+    <row r="26" ht="37.5" spans="1:6">
       <c r="A26" s="5">
         <v>9</v>
       </c>
@@ -15322,7 +15319,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" ht="56" spans="1:6">
+    <row r="27" ht="57" spans="1:6">
       <c r="A27" s="5">
         <v>10</v>
       </c>
@@ -15342,7 +15339,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" ht="56" spans="1:6">
+    <row r="28" ht="57" spans="1:6">
       <c r="A28" s="5">
         <v>11</v>
       </c>
@@ -15360,7 +15357,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" ht="35" spans="1:6">
+    <row r="29" ht="37.5" spans="1:6">
       <c r="A29" s="5">
         <v>12</v>
       </c>
@@ -15380,7 +15377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" ht="35" spans="1:6">
+    <row r="30" ht="37.5" spans="1:6">
       <c r="A30" s="5">
         <v>13</v>
       </c>
@@ -15398,7 +15395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" ht="35" spans="1:6">
+    <row r="31" ht="37.5" spans="1:6">
       <c r="A31" s="5">
         <v>14</v>
       </c>
@@ -15416,7 +15413,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" ht="35" spans="1:6">
+    <row r="32" ht="37.5" spans="1:6">
       <c r="A32" s="5">
         <v>15</v>
       </c>
@@ -15434,7 +15431,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" ht="35" spans="1:6">
+    <row r="33" ht="37.5" spans="1:6">
       <c r="A33" s="5">
         <v>16</v>
       </c>
@@ -15452,7 +15449,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" ht="35" spans="1:6">
+    <row r="34" ht="37.5" spans="1:6">
       <c r="A34" s="5">
         <v>17</v>
       </c>
@@ -15470,7 +15467,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" ht="35" spans="1:6">
+    <row r="35" ht="37.5" spans="1:6">
       <c r="A35" s="5">
         <v>18</v>
       </c>
@@ -15488,7 +15485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" ht="35" spans="1:6">
+    <row r="36" ht="37.5" spans="1:6">
       <c r="A36" s="5">
         <v>19</v>
       </c>
@@ -15506,7 +15503,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" ht="35" spans="1:6">
+    <row r="37" ht="37.5" spans="1:6">
       <c r="A37" s="5">
         <v>20</v>
       </c>
@@ -15524,7 +15521,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" ht="35" spans="1:6">
+    <row r="38" ht="37.5" spans="1:6">
       <c r="A38" s="5">
         <v>21</v>
       </c>
@@ -15542,7 +15539,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" ht="35" spans="1:6">
+    <row r="39" ht="37.5" spans="1:6">
       <c r="A39" s="5">
         <v>22</v>
       </c>
@@ -15560,7 +15557,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" ht="35" spans="1:6">
+    <row r="40" ht="37.5" spans="1:6">
       <c r="A40" s="5">
         <v>23</v>
       </c>
@@ -15578,7 +15575,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" ht="35" spans="1:6">
+    <row r="41" ht="37.5" spans="1:6">
       <c r="A41" s="5">
         <v>24</v>
       </c>
@@ -15598,7 +15595,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" ht="35" spans="1:6">
+    <row r="42" ht="37.5" spans="1:6">
       <c r="A42" s="5">
         <v>25</v>
       </c>
@@ -15618,7 +15615,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" ht="56" spans="1:6">
+    <row r="43" ht="57" spans="1:6">
       <c r="A43" s="5">
         <v>26</v>
       </c>
@@ -15638,7 +15635,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" ht="56" spans="1:6">
+    <row r="44" ht="57" spans="1:6">
       <c r="A44" s="5">
         <v>27</v>
       </c>
@@ -15658,7 +15655,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" ht="56" spans="1:6">
+    <row r="45" ht="57" spans="1:6">
       <c r="A45" s="5">
         <v>28</v>
       </c>
@@ -15678,7 +15675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" ht="56" spans="1:6">
+    <row r="46" ht="57" spans="1:6">
       <c r="A46" s="5">
         <v>29</v>
       </c>
@@ -15698,7 +15695,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" ht="56" spans="1:6">
+    <row r="47" ht="57" spans="1:6">
       <c r="A47" s="5">
         <v>30</v>
       </c>
@@ -15718,7 +15715,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" ht="56" spans="1:6">
+    <row r="48" ht="57" spans="1:6">
       <c r="A48" s="5">
         <v>31</v>
       </c>
@@ -15738,7 +15735,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" ht="56" spans="1:6">
+    <row r="49" ht="57" spans="1:6">
       <c r="A49" s="5">
         <v>32</v>
       </c>
@@ -15758,7 +15755,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" ht="56" spans="1:6">
+    <row r="50" ht="57" spans="1:6">
       <c r="A50" s="5">
         <v>33</v>
       </c>
@@ -15778,7 +15775,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" ht="56" spans="1:6">
+    <row r="51" ht="57" spans="1:6">
       <c r="A51" s="5">
         <v>34</v>
       </c>
@@ -15798,7 +15795,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" ht="35" spans="1:6">
+    <row r="52" ht="37.5" spans="1:6">
       <c r="A52" s="5">
         <v>35</v>
       </c>
@@ -15818,49 +15815,49 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1048516" customFormat="1" ht="14"/>
-    <row r="1048517" customFormat="1" ht="14"/>
-    <row r="1048518" customFormat="1" ht="14"/>
-    <row r="1048519" customFormat="1" ht="14"/>
-    <row r="1048520" customFormat="1" ht="14"/>
-    <row r="1048521" customFormat="1" ht="14"/>
-    <row r="1048522" customFormat="1" ht="14"/>
-    <row r="1048523" customFormat="1" ht="14"/>
-    <row r="1048524" customFormat="1" ht="14"/>
-    <row r="1048525" customFormat="1" ht="14"/>
-    <row r="1048526" customFormat="1" ht="14"/>
-    <row r="1048527" customFormat="1" ht="14"/>
-    <row r="1048528" customFormat="1" ht="14"/>
-    <row r="1048529" customFormat="1" ht="14"/>
-    <row r="1048530" customFormat="1" ht="14"/>
-    <row r="1048531" customFormat="1" ht="14"/>
-    <row r="1048532" customFormat="1" ht="14"/>
-    <row r="1048533" customFormat="1" ht="14"/>
-    <row r="1048534" customFormat="1" ht="14"/>
-    <row r="1048535" customFormat="1" ht="14"/>
-    <row r="1048536" customFormat="1" ht="14"/>
-    <row r="1048537" customFormat="1" ht="14"/>
-    <row r="1048538" customFormat="1" ht="14"/>
-    <row r="1048539" customFormat="1" ht="14"/>
-    <row r="1048540" customFormat="1" ht="14"/>
-    <row r="1048541" customFormat="1" ht="14"/>
-    <row r="1048542" customFormat="1" ht="14"/>
-    <row r="1048543" customFormat="1" ht="14"/>
-    <row r="1048544" customFormat="1" ht="14"/>
-    <row r="1048545" customFormat="1" ht="14"/>
-    <row r="1048546" customFormat="1" ht="14"/>
-    <row r="1048547" customFormat="1" ht="14"/>
-    <row r="1048548" customFormat="1" ht="14"/>
-    <row r="1048549" customFormat="1" ht="14"/>
-    <row r="1048550" customFormat="1" ht="14"/>
-    <row r="1048551" customFormat="1" ht="14"/>
-    <row r="1048552" customFormat="1" ht="14"/>
-    <row r="1048553" customFormat="1" ht="14"/>
-    <row r="1048554" customFormat="1" ht="14"/>
-    <row r="1048555" customFormat="1" ht="14"/>
-    <row r="1048556" customFormat="1" ht="14"/>
-    <row r="1048557" customFormat="1" ht="14"/>
-    <row r="1048558" customFormat="1" ht="14"/>
+    <row r="1048516" customFormat="1" ht="14.25"/>
+    <row r="1048517" customFormat="1" ht="14.25"/>
+    <row r="1048518" customFormat="1" ht="14.25"/>
+    <row r="1048519" customFormat="1" ht="14.25"/>
+    <row r="1048520" customFormat="1" ht="14.25"/>
+    <row r="1048521" customFormat="1" ht="14.25"/>
+    <row r="1048522" customFormat="1" ht="14.25"/>
+    <row r="1048523" customFormat="1" ht="14.25"/>
+    <row r="1048524" customFormat="1" ht="14.25"/>
+    <row r="1048525" customFormat="1" ht="14.25"/>
+    <row r="1048526" customFormat="1" ht="14.25"/>
+    <row r="1048527" customFormat="1" ht="14.25"/>
+    <row r="1048528" customFormat="1" ht="14.25"/>
+    <row r="1048529" customFormat="1" ht="14.25"/>
+    <row r="1048530" customFormat="1" ht="14.25"/>
+    <row r="1048531" customFormat="1" ht="14.25"/>
+    <row r="1048532" customFormat="1" ht="14.25"/>
+    <row r="1048533" customFormat="1" ht="14.25"/>
+    <row r="1048534" customFormat="1" ht="14.25"/>
+    <row r="1048535" customFormat="1" ht="14.25"/>
+    <row r="1048536" customFormat="1" ht="14.25"/>
+    <row r="1048537" customFormat="1" ht="14.25"/>
+    <row r="1048538" customFormat="1" ht="14.25"/>
+    <row r="1048539" customFormat="1" ht="14.25"/>
+    <row r="1048540" customFormat="1" ht="14.25"/>
+    <row r="1048541" customFormat="1" ht="14.25"/>
+    <row r="1048542" customFormat="1" ht="14.25"/>
+    <row r="1048543" customFormat="1" ht="14.25"/>
+    <row r="1048544" customFormat="1" ht="14.25"/>
+    <row r="1048545" customFormat="1" ht="14.25"/>
+    <row r="1048546" customFormat="1" ht="14.25"/>
+    <row r="1048547" customFormat="1" ht="14.25"/>
+    <row r="1048548" customFormat="1" ht="14.25"/>
+    <row r="1048549" customFormat="1" ht="14.25"/>
+    <row r="1048550" customFormat="1" ht="14.25"/>
+    <row r="1048551" customFormat="1" ht="14.25"/>
+    <row r="1048552" customFormat="1" ht="14.25"/>
+    <row r="1048553" customFormat="1" ht="14.25"/>
+    <row r="1048554" customFormat="1" ht="14.25"/>
+    <row r="1048555" customFormat="1" ht="14.25"/>
+    <row r="1048556" customFormat="1" ht="14.25"/>
+    <row r="1048557" customFormat="1" ht="14.25"/>
+    <row r="1048558" customFormat="1" ht="14.25"/>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A7:A8"/>
@@ -15883,14 +15880,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="F7:H12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="6" max="6" width="16.75" customWidth="1"/>
     <col min="7" max="7" width="8.75" customWidth="1"/>
     <col min="8" max="8" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" ht="17.5" spans="6:8">
+    <row r="7" ht="18.75" spans="6:8">
       <c r="F7" s="2" t="s">
         <v>301</v>
       </c>
@@ -15901,7 +15898,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="8" ht="17.5" spans="6:8">
+    <row r="8" ht="18.75" spans="6:8">
       <c r="F8" s="1" t="s">
         <v>304</v>
       </c>
@@ -15912,7 +15909,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="9" ht="17.5" spans="6:8">
+    <row r="9" ht="18.75" spans="6:8">
       <c r="F9" s="1" t="s">
         <v>307</v>
       </c>
@@ -15923,7 +15920,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="10" ht="17.5" spans="6:8">
+    <row r="10" ht="18.75" spans="6:8">
       <c r="F10" s="1" t="s">
         <v>310</v>
       </c>
@@ -15934,7 +15931,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="11" ht="17.5" spans="6:8">
+    <row r="11" ht="18.75" spans="6:8">
       <c r="F11" s="1" t="s">
         <v>313</v>
       </c>
@@ -15945,7 +15942,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="12" ht="17.5" spans="6:8">
+    <row r="12" ht="18.75" spans="6:8">
       <c r="F12" s="1" t="s">
         <v>316</v>
       </c>
@@ -15966,7 +15963,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G195"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="1" customWidth="1"/>
@@ -32354,7 +32351,7 @@
     <col min="16384" max="16384" width="65.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" spans="1:5">
+    <row r="1" ht="37.5" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -32371,7 +32368,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="2" ht="35" spans="1:5">
+    <row r="2" ht="37.5" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -32388,7 +32385,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="3" ht="35" spans="1:5">
+    <row r="3" ht="37.5" spans="1:5">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -32405,7 +32402,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="4" ht="35" spans="1:5">
+    <row r="4" ht="37.5" spans="1:5">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -32422,7 +32419,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="5" ht="35" spans="1:5">
+    <row r="5" ht="37.5" spans="1:5">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -32439,7 +32436,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="11" ht="35" spans="1:5">
+    <row r="11" ht="37.5" spans="1:5">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -32456,7 +32453,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="12" ht="52.5" spans="1:5">
+    <row r="12" ht="56.25" spans="1:5">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -32473,7 +32470,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="13" ht="52.5" spans="1:5">
+    <row r="13" ht="56.25" spans="1:5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -32490,7 +32487,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="14" ht="35" spans="1:5">
+    <row r="14" ht="37.5" spans="1:5">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -32507,7 +32504,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="15" ht="35" spans="1:5">
+    <row r="15" ht="37.5" spans="1:5">
       <c r="A15" s="1">
         <v>4</v>
       </c>
@@ -32524,7 +32521,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="16" ht="35" spans="1:5">
+    <row r="16" ht="37.5" spans="1:5">
       <c r="A16" s="1">
         <v>5</v>
       </c>
@@ -32541,7 +32538,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="17" ht="35" spans="1:5">
+    <row r="17" ht="37.5" spans="1:5">
       <c r="A17" s="1">
         <v>6</v>
       </c>
@@ -32558,7 +32555,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="18" ht="35" spans="1:5">
+    <row r="18" ht="37.5" spans="1:5">
       <c r="A18" s="1">
         <v>7</v>
       </c>
@@ -32575,7 +32572,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="19" ht="35" spans="1:5">
+    <row r="19" ht="37.5" spans="1:5">
       <c r="A19" s="1">
         <v>8</v>
       </c>
@@ -32592,7 +32589,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="20" ht="35" spans="1:5">
+    <row r="20" ht="37.5" spans="1:5">
       <c r="A20" s="1">
         <v>9</v>
       </c>
@@ -32609,7 +32606,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="21" ht="35" spans="1:5">
+    <row r="21" ht="37.5" spans="1:5">
       <c r="A21" s="1">
         <v>10</v>
       </c>
@@ -32626,7 +32623,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="22" ht="52.5" spans="1:5">
+    <row r="22" ht="56.25" spans="1:5">
       <c r="A22" s="1">
         <v>11</v>
       </c>
@@ -32643,7 +32640,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="23" ht="52.5" spans="1:5">
+    <row r="23" ht="56.25" spans="1:5">
       <c r="A23" s="1">
         <v>12</v>
       </c>
@@ -32660,7 +32657,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="24" ht="52.5" spans="1:5">
+    <row r="24" ht="56.25" spans="1:5">
       <c r="A24" s="1">
         <v>13</v>
       </c>
@@ -32677,7 +32674,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="25" ht="35" spans="1:5">
+    <row r="25" ht="37.5" spans="1:5">
       <c r="A25" s="1">
         <v>14</v>
       </c>
@@ -32694,7 +32691,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="26" ht="35" spans="1:5">
+    <row r="26" ht="37.5" spans="1:5">
       <c r="A26" s="1">
         <v>15</v>
       </c>
@@ -32711,7 +32708,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="27" ht="35" spans="1:5">
+    <row r="27" ht="37.5" spans="1:5">
       <c r="A27" s="1">
         <v>16</v>
       </c>
@@ -32728,7 +32725,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="28" ht="35" spans="1:5">
+    <row r="28" ht="37.5" spans="1:5">
       <c r="A28" s="1">
         <v>17</v>
       </c>
@@ -32745,7 +32742,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="29" ht="35" spans="1:5">
+    <row r="29" ht="37.5" spans="1:5">
       <c r="A29" s="1">
         <v>18</v>
       </c>
@@ -32762,7 +32759,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="30" ht="35" spans="1:5">
+    <row r="30" ht="37.5" spans="1:5">
       <c r="A30" s="1">
         <v>19</v>
       </c>
@@ -32779,7 +32776,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="31" ht="35" spans="1:5">
+    <row r="31" ht="37.5" spans="1:5">
       <c r="A31" s="1">
         <v>20</v>
       </c>
@@ -32796,7 +32793,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="32" ht="52.5" spans="1:5">
+    <row r="32" ht="56.25" spans="1:5">
       <c r="A32" s="1">
         <v>22</v>
       </c>
@@ -32813,7 +32810,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="33" ht="52.5" spans="1:5">
+    <row r="33" ht="56.25" spans="1:5">
       <c r="A33" s="1">
         <v>23</v>
       </c>
@@ -32830,7 +32827,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="34" ht="52.5" spans="1:5">
+    <row r="34" ht="56.25" spans="1:5">
       <c r="A34" s="1">
         <v>24</v>
       </c>
@@ -32847,7 +32844,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="35" ht="52.5" spans="1:5">
+    <row r="35" ht="56.25" spans="1:5">
       <c r="A35" s="1">
         <v>25</v>
       </c>
@@ -32864,7 +32861,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="36" ht="52.5" spans="1:5">
+    <row r="36" ht="56.25" spans="1:5">
       <c r="A36" s="1">
         <v>26</v>
       </c>
@@ -32881,7 +32878,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="37" ht="52.5" spans="1:5">
+    <row r="37" ht="56.25" spans="1:5">
       <c r="A37" s="1">
         <v>27</v>
       </c>
@@ -32898,7 +32895,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="38" ht="52.5" spans="1:5">
+    <row r="38" ht="56.25" spans="1:5">
       <c r="A38" s="1">
         <v>28</v>
       </c>
@@ -32915,7 +32912,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="39" ht="52.5" spans="1:5">
+    <row r="39" ht="56.25" spans="1:5">
       <c r="A39" s="1">
         <v>30</v>
       </c>
@@ -32932,7 +32929,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="40" ht="52.5" spans="1:5">
+    <row r="40" ht="56.25" spans="1:5">
       <c r="A40" s="1">
         <v>31</v>
       </c>
@@ -32949,7 +32946,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="41" ht="52.5" spans="1:5">
+    <row r="41" ht="56.25" spans="1:5">
       <c r="A41" s="1">
         <v>32</v>
       </c>
@@ -32966,7 +32963,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="42" ht="52.5" spans="1:5">
+    <row r="42" ht="56.25" spans="1:5">
       <c r="A42" s="1">
         <v>33</v>
       </c>
@@ -32983,7 +32980,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="43" ht="52.5" spans="1:5">
+    <row r="43" ht="56.25" spans="1:5">
       <c r="A43" s="1">
         <v>34</v>
       </c>
@@ -33000,7 +32997,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="44" ht="52.5" spans="1:5">
+    <row r="44" ht="56.25" spans="1:5">
       <c r="A44" s="1">
         <v>35</v>
       </c>
@@ -33017,7 +33014,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="45" ht="52.5" spans="1:5">
+    <row r="45" ht="56.25" spans="1:5">
       <c r="A45" s="1">
         <v>36</v>
       </c>
@@ -33034,7 +33031,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="46" ht="52.5" spans="1:5">
+    <row r="46" ht="56.25" spans="1:5">
       <c r="A46" s="1">
         <v>37</v>
       </c>
@@ -33051,7 +33048,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="47" ht="52.5" spans="1:5">
+    <row r="47" ht="56.25" spans="1:5">
       <c r="A47" s="1">
         <v>38</v>
       </c>
@@ -33068,7 +33065,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="48" ht="52.5" spans="1:5">
+    <row r="48" ht="56.25" spans="1:5">
       <c r="A48" s="1">
         <v>39</v>
       </c>
@@ -33085,7 +33082,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="49" ht="52.5" spans="1:5">
+    <row r="49" ht="56.25" spans="1:5">
       <c r="A49" s="1">
         <v>40</v>
       </c>
@@ -33102,7 +33099,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="50" ht="52.5" spans="1:5">
+    <row r="50" ht="56.25" spans="1:5">
       <c r="A50" s="1">
         <v>41</v>
       </c>
@@ -33119,7 +33116,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="51" ht="35" spans="1:5">
+    <row r="51" ht="37.5" spans="1:5">
       <c r="A51" s="1">
         <v>42</v>
       </c>
@@ -33136,7 +33133,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="52" ht="35" spans="1:5">
+    <row r="52" ht="37.5" spans="1:5">
       <c r="A52" s="1">
         <v>43</v>
       </c>
@@ -33153,7 +33150,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="53" ht="35" spans="1:5">
+    <row r="53" ht="37.5" spans="1:5">
       <c r="A53" s="1">
         <v>44</v>
       </c>
@@ -33170,7 +33167,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="54" ht="35" spans="1:5">
+    <row r="54" ht="37.5" spans="1:5">
       <c r="A54" s="1">
         <v>45</v>
       </c>
@@ -33187,7 +33184,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="55" ht="35" spans="1:5">
+    <row r="55" ht="37.5" spans="1:5">
       <c r="A55" s="1">
         <v>46</v>
       </c>
@@ -33204,7 +33201,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="56" ht="35" spans="1:5">
+    <row r="56" ht="37.5" spans="1:5">
       <c r="A56" s="1">
         <v>47</v>
       </c>
@@ -33221,7 +33218,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="57" ht="35" spans="1:5">
+    <row r="57" ht="37.5" spans="1:5">
       <c r="A57" s="1">
         <v>48</v>
       </c>
@@ -33238,7 +33235,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="58" ht="35" spans="1:5">
+    <row r="58" ht="37.5" spans="1:5">
       <c r="A58" s="1">
         <v>49</v>
       </c>
@@ -33255,7 +33252,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="59" ht="35" spans="1:5">
+    <row r="59" ht="37.5" spans="1:5">
       <c r="A59" s="1">
         <v>50</v>
       </c>
@@ -33272,7 +33269,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="60" ht="35" spans="1:5">
+    <row r="60" ht="37.5" spans="1:5">
       <c r="A60" s="1">
         <v>51</v>
       </c>
@@ -33289,7 +33286,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="61" ht="35" spans="1:5">
+    <row r="61" ht="37.5" spans="1:5">
       <c r="A61" s="1">
         <v>52</v>
       </c>
@@ -33306,7 +33303,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="62" ht="35" spans="1:5">
+    <row r="62" ht="37.5" spans="1:5">
       <c r="A62" s="1">
         <v>53</v>
       </c>
@@ -33323,7 +33320,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="63" ht="35" spans="1:5">
+    <row r="63" ht="37.5" spans="1:5">
       <c r="A63" s="1">
         <v>54</v>
       </c>
@@ -33340,7 +33337,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="64" ht="35" spans="1:5">
+    <row r="64" ht="37.5" spans="1:5">
       <c r="A64" s="1">
         <v>55</v>
       </c>
@@ -33357,7 +33354,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="65" ht="35" spans="1:5">
+    <row r="65" ht="37.5" spans="1:5">
       <c r="A65" s="1">
         <v>56</v>
       </c>
@@ -33374,7 +33371,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="66" ht="35" spans="1:5">
+    <row r="66" ht="37.5" spans="1:5">
       <c r="A66" s="1">
         <v>57</v>
       </c>
@@ -33391,7 +33388,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="67" ht="35" spans="1:5">
+    <row r="67" ht="37.5" spans="1:5">
       <c r="A67" s="1">
         <v>58</v>
       </c>
@@ -33408,7 +33405,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="68" ht="35" spans="1:5">
+    <row r="68" ht="37.5" spans="1:5">
       <c r="A68" s="1">
         <v>59</v>
       </c>
@@ -33425,7 +33422,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="69" ht="35" spans="1:5">
+    <row r="69" ht="37.5" spans="1:5">
       <c r="A69" s="1">
         <v>60</v>
       </c>
@@ -33442,7 +33439,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="70" ht="35" spans="1:5">
+    <row r="70" ht="37.5" spans="1:5">
       <c r="A70" s="1">
         <v>61</v>
       </c>
@@ -33459,7 +33456,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="71" ht="35" spans="1:5">
+    <row r="71" ht="37.5" spans="1:5">
       <c r="A71" s="1">
         <v>62</v>
       </c>
@@ -33476,7 +33473,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="72" ht="35" spans="1:5">
+    <row r="72" ht="37.5" spans="1:5">
       <c r="A72" s="1">
         <v>63</v>
       </c>
@@ -33493,7 +33490,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="73" ht="35" spans="1:5">
+    <row r="73" ht="37.5" spans="1:5">
       <c r="A73" s="1">
         <v>64</v>
       </c>
@@ -33510,7 +33507,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="74" ht="35" spans="1:5">
+    <row r="74" ht="37.5" spans="1:5">
       <c r="A74" s="1">
         <v>65</v>
       </c>
@@ -33527,7 +33524,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="75" ht="35" spans="1:5">
+    <row r="75" ht="37.5" spans="1:5">
       <c r="A75" s="1">
         <v>66</v>
       </c>
@@ -33544,7 +33541,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="76" ht="35" spans="1:5">
+    <row r="76" ht="37.5" spans="1:5">
       <c r="A76" s="1">
         <v>67</v>
       </c>
@@ -33561,7 +33558,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="77" ht="35" spans="1:5">
+    <row r="77" ht="37.5" spans="1:5">
       <c r="A77" s="1">
         <v>68</v>
       </c>
@@ -33578,7 +33575,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="78" ht="35" spans="1:5">
+    <row r="78" ht="37.5" spans="1:5">
       <c r="A78" s="1">
         <v>69</v>
       </c>
@@ -33595,7 +33592,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="79" ht="35" spans="1:5">
+    <row r="79" ht="37.5" spans="1:5">
       <c r="A79" s="1">
         <v>70</v>
       </c>
@@ -33612,7 +33609,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="80" ht="35" spans="1:5">
+    <row r="80" ht="37.5" spans="1:5">
       <c r="A80" s="1">
         <v>71</v>
       </c>
@@ -33629,7 +33626,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="81" ht="35" spans="1:5">
+    <row r="81" ht="37.5" spans="1:5">
       <c r="A81" s="1">
         <v>72</v>
       </c>
@@ -33646,7 +33643,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="82" ht="35" spans="1:5">
+    <row r="82" ht="37.5" spans="1:5">
       <c r="A82" s="1">
         <v>73</v>
       </c>
@@ -33663,7 +33660,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="83" ht="35" spans="1:5">
+    <row r="83" ht="37.5" spans="1:5">
       <c r="A83" s="1">
         <v>74</v>
       </c>
@@ -33680,7 +33677,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="84" ht="35" spans="1:5">
+    <row r="84" ht="37.5" spans="1:5">
       <c r="A84" s="1">
         <v>75</v>
       </c>
@@ -33697,7 +33694,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="85" ht="35" spans="1:5">
+    <row r="85" ht="37.5" spans="1:5">
       <c r="A85" s="1">
         <v>76</v>
       </c>
@@ -33714,7 +33711,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="86" ht="35" spans="1:5">
+    <row r="86" ht="37.5" spans="1:5">
       <c r="A86" s="1">
         <v>77</v>
       </c>
@@ -33731,7 +33728,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="87" ht="35" spans="1:5">
+    <row r="87" ht="37.5" spans="1:5">
       <c r="A87" s="1">
         <v>78</v>
       </c>
@@ -33748,7 +33745,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="88" ht="35" spans="1:5">
+    <row r="88" ht="37.5" spans="1:5">
       <c r="A88" s="1">
         <v>79</v>
       </c>
@@ -33765,7 +33762,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="89" ht="35" spans="1:5">
+    <row r="89" ht="37.5" spans="1:5">
       <c r="A89" s="1">
         <v>80</v>
       </c>
@@ -33782,7 +33779,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="90" ht="35" spans="1:5">
+    <row r="90" ht="37.5" spans="1:5">
       <c r="A90" s="1">
         <v>81</v>
       </c>
@@ -33799,7 +33796,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="91" ht="35" spans="1:5">
+    <row r="91" ht="37.5" spans="1:5">
       <c r="A91" s="1">
         <v>82</v>
       </c>
@@ -33816,7 +33813,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="92" ht="35" spans="1:5">
+    <row r="92" ht="37.5" spans="1:5">
       <c r="A92" s="1">
         <v>83</v>
       </c>
@@ -33833,7 +33830,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="93" ht="35" spans="1:5">
+    <row r="93" ht="37.5" spans="1:5">
       <c r="A93" s="1">
         <v>84</v>
       </c>
@@ -33850,7 +33847,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="94" ht="35" spans="1:5">
+    <row r="94" ht="37.5" spans="1:5">
       <c r="A94" s="1">
         <v>85</v>
       </c>
@@ -33867,7 +33864,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="95" ht="35" spans="1:5">
+    <row r="95" ht="37.5" spans="1:5">
       <c r="A95" s="1">
         <v>86</v>
       </c>
@@ -33884,7 +33881,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="96" ht="35" spans="1:5">
+    <row r="96" ht="37.5" spans="1:5">
       <c r="A96" s="1">
         <v>88</v>
       </c>
@@ -33901,7 +33898,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="97" ht="35" spans="1:5">
+    <row r="97" ht="37.5" spans="1:5">
       <c r="A97" s="1">
         <v>89</v>
       </c>
@@ -33918,7 +33915,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="98" ht="35" spans="1:5">
+    <row r="98" ht="37.5" spans="1:5">
       <c r="A98" s="1">
         <v>90</v>
       </c>
@@ -33935,7 +33932,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="99" ht="35" spans="1:5">
+    <row r="99" ht="37.5" spans="1:5">
       <c r="A99" s="1">
         <v>91</v>
       </c>
@@ -33952,7 +33949,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="100" ht="35" spans="1:5">
+    <row r="100" ht="37.5" spans="1:5">
       <c r="A100" s="1">
         <v>92</v>
       </c>
@@ -33969,7 +33966,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="101" ht="35" spans="1:5">
+    <row r="101" ht="37.5" spans="1:5">
       <c r="A101" s="1">
         <v>93</v>
       </c>
@@ -33986,7 +33983,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="102" ht="35" spans="1:5">
+    <row r="102" ht="37.5" spans="1:5">
       <c r="A102" s="1">
         <v>94</v>
       </c>
@@ -34003,7 +34000,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="103" ht="35" spans="1:5">
+    <row r="103" ht="37.5" spans="1:5">
       <c r="A103" s="1">
         <v>95</v>
       </c>
@@ -34020,7 +34017,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="104" ht="35" spans="1:5">
+    <row r="104" ht="37.5" spans="1:5">
       <c r="A104" s="1">
         <v>96</v>
       </c>
@@ -34037,7 +34034,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="105" ht="35" spans="1:5">
+    <row r="105" ht="37.5" spans="1:5">
       <c r="A105" s="1">
         <v>97</v>
       </c>
@@ -34054,7 +34051,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="106" ht="35" spans="1:5">
+    <row r="106" ht="37.5" spans="1:5">
       <c r="A106" s="1">
         <v>98</v>
       </c>
@@ -34071,7 +34068,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="107" ht="35" spans="1:5">
+    <row r="107" ht="37.5" spans="1:5">
       <c r="A107" s="1">
         <v>99</v>
       </c>
@@ -34088,7 +34085,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="108" ht="35" spans="1:5">
+    <row r="108" ht="37.5" spans="1:5">
       <c r="A108" s="1">
         <v>100</v>
       </c>
@@ -34105,7 +34102,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="109" ht="35" spans="1:5">
+    <row r="109" ht="37.5" spans="1:5">
       <c r="A109" s="1">
         <v>101</v>
       </c>
@@ -34122,7 +34119,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="110" ht="35" spans="1:5">
+    <row r="110" ht="37.5" spans="1:5">
       <c r="A110" s="1">
         <v>102</v>
       </c>
@@ -34139,7 +34136,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="111" ht="35" spans="1:5">
+    <row r="111" ht="37.5" spans="1:5">
       <c r="A111" s="1">
         <v>103</v>
       </c>
@@ -34156,7 +34153,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="112" ht="35" spans="1:5">
+    <row r="112" ht="37.5" spans="1:5">
       <c r="A112" s="1">
         <v>104</v>
       </c>
@@ -34173,7 +34170,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="113" ht="35" spans="1:5">
+    <row r="113" ht="37.5" spans="1:5">
       <c r="A113" s="1">
         <v>105</v>
       </c>
@@ -34190,7 +34187,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="114" ht="35" spans="1:5">
+    <row r="114" ht="37.5" spans="1:5">
       <c r="A114" s="1">
         <v>106</v>
       </c>
@@ -34207,7 +34204,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="115" ht="35" spans="1:5">
+    <row r="115" ht="37.5" spans="1:5">
       <c r="A115" s="1">
         <v>107</v>
       </c>
@@ -34224,7 +34221,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="116" ht="35" spans="1:5">
+    <row r="116" ht="37.5" spans="1:5">
       <c r="A116" s="1">
         <v>108</v>
       </c>
@@ -34241,7 +34238,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="117" ht="35" spans="1:5">
+    <row r="117" ht="37.5" spans="1:5">
       <c r="A117" s="1">
         <v>109</v>
       </c>
@@ -34258,7 +34255,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="118" ht="35" spans="1:5">
+    <row r="118" ht="37.5" spans="1:5">
       <c r="A118" s="1">
         <v>110</v>
       </c>
@@ -34275,7 +34272,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="119" ht="35" spans="1:5">
+    <row r="119" ht="37.5" spans="1:5">
       <c r="A119" s="1">
         <v>111</v>
       </c>
@@ -34292,7 +34289,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="120" ht="35" spans="1:5">
+    <row r="120" ht="37.5" spans="1:5">
       <c r="A120" s="1">
         <v>112</v>
       </c>
@@ -34309,7 +34306,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="121" ht="35" spans="1:5">
+    <row r="121" ht="37.5" spans="1:5">
       <c r="A121" s="1">
         <v>113</v>
       </c>
@@ -34326,7 +34323,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="122" ht="35" spans="1:5">
+    <row r="122" ht="37.5" spans="1:5">
       <c r="A122" s="1">
         <v>114</v>
       </c>
@@ -34343,7 +34340,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="123" ht="35" spans="1:5">
+    <row r="123" ht="37.5" spans="1:5">
       <c r="A123" s="1">
         <v>115</v>
       </c>
@@ -34360,7 +34357,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="124" ht="35" spans="1:5">
+    <row r="124" ht="37.5" spans="1:5">
       <c r="A124" s="1">
         <v>116</v>
       </c>
@@ -34377,7 +34374,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="125" ht="35" spans="1:5">
+    <row r="125" ht="37.5" spans="1:5">
       <c r="A125" s="1">
         <v>117</v>
       </c>
@@ -34394,7 +34391,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="126" ht="35" spans="1:5">
+    <row r="126" ht="37.5" spans="1:5">
       <c r="A126" s="1">
         <v>118</v>
       </c>
@@ -34411,7 +34408,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="127" ht="35" spans="1:5">
+    <row r="127" ht="37.5" spans="1:5">
       <c r="A127" s="1">
         <v>119</v>
       </c>
@@ -34428,7 +34425,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="128" ht="35" spans="1:5">
+    <row r="128" ht="37.5" spans="1:5">
       <c r="A128" s="1">
         <v>120</v>
       </c>
@@ -34445,7 +34442,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="129" ht="35" spans="1:5">
+    <row r="129" ht="37.5" spans="1:5">
       <c r="A129" s="1">
         <v>121</v>
       </c>
@@ -34470,7 +34467,7 @@
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
     </row>
-    <row r="132" ht="87.5" spans="1:7">
+    <row r="132" ht="93.75" spans="1:7">
       <c r="A132" s="2" t="s">
         <v>0</v>
       </c>
@@ -34493,7 +34490,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="133" ht="35" spans="1:6">
+    <row r="133" ht="37.5" spans="1:6">
       <c r="A133" s="1">
         <v>1</v>
       </c>
@@ -34513,7 +34510,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="134" ht="70" spans="1:6">
+    <row r="134" ht="75" spans="1:6">
       <c r="A134" s="1">
         <v>2</v>
       </c>
@@ -34533,7 +34530,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="135" ht="70" spans="1:7">
+    <row r="135" ht="75" spans="1:7">
       <c r="A135" s="1">
         <v>3</v>
       </c>
@@ -34556,7 +34553,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="136" ht="35" spans="1:6">
+    <row r="136" ht="37.5" spans="1:6">
       <c r="A136" s="1">
         <v>4</v>
       </c>
@@ -34576,7 +34573,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="137" ht="35" spans="1:6">
+    <row r="137" ht="37.5" spans="1:6">
       <c r="A137" s="1">
         <v>5</v>
       </c>
@@ -34596,7 +34593,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="138" ht="70" spans="1:6">
+    <row r="138" ht="75" spans="1:6">
       <c r="A138" s="1">
         <v>6</v>
       </c>
@@ -34616,7 +34613,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="139" ht="35" spans="1:6">
+    <row r="139" ht="37.5" spans="1:6">
       <c r="A139" s="1">
         <v>8</v>
       </c>
@@ -34636,7 +34633,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="140" ht="35" spans="1:6">
+    <row r="140" ht="37.5" spans="1:6">
       <c r="A140" s="1">
         <v>9</v>
       </c>
@@ -34656,7 +34653,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="141" ht="35" spans="1:6">
+    <row r="141" ht="37.5" spans="1:6">
       <c r="A141" s="1">
         <v>10</v>
       </c>
@@ -34676,7 +34673,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="142" ht="35" spans="1:6">
+    <row r="142" ht="37.5" spans="1:6">
       <c r="A142" s="1">
         <v>11</v>
       </c>
@@ -34696,7 +34693,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="143" ht="35" spans="1:5">
+    <row r="143" ht="37.5" spans="1:5">
       <c r="A143" s="1">
         <v>12</v>
       </c>
@@ -34713,7 +34710,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="144" ht="35" spans="1:5">
+    <row r="144" ht="37.5" spans="1:5">
       <c r="A144" s="1">
         <v>13</v>
       </c>
@@ -34730,7 +34727,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="145" ht="35" spans="1:5">
+    <row r="145" ht="37.5" spans="1:5">
       <c r="A145" s="1">
         <v>14</v>
       </c>
@@ -34747,7 +34744,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="146" ht="35" spans="1:5">
+    <row r="146" ht="37.5" spans="1:5">
       <c r="A146" s="1">
         <v>15</v>
       </c>
@@ -34764,7 +34761,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="147" ht="35" spans="1:5">
+    <row r="147" ht="37.5" spans="1:5">
       <c r="A147" s="1">
         <v>16</v>
       </c>
@@ -34781,7 +34778,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="148" ht="35" spans="1:5">
+    <row r="148" ht="37.5" spans="1:5">
       <c r="A148" s="1">
         <v>17</v>
       </c>
@@ -34798,7 +34795,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="149" ht="35" spans="1:5">
+    <row r="149" ht="37.5" spans="1:5">
       <c r="A149" s="1">
         <v>18</v>
       </c>
@@ -34815,7 +34812,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="150" ht="35" spans="1:5">
+    <row r="150" ht="37.5" spans="1:5">
       <c r="A150" s="1">
         <v>19</v>
       </c>
@@ -34832,7 +34829,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="151" ht="35" spans="1:5">
+    <row r="151" ht="37.5" spans="1:5">
       <c r="A151" s="1">
         <v>20</v>
       </c>
@@ -34849,7 +34846,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="152" ht="35" spans="1:5">
+    <row r="152" ht="37.5" spans="1:5">
       <c r="A152" s="1">
         <v>21</v>
       </c>
@@ -34866,7 +34863,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="153" ht="35" spans="1:5">
+    <row r="153" ht="37.5" spans="1:5">
       <c r="A153" s="1">
         <v>22</v>
       </c>
@@ -34883,7 +34880,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="154" ht="35" spans="1:5">
+    <row r="154" ht="37.5" spans="1:5">
       <c r="A154" s="1">
         <v>23</v>
       </c>
@@ -34900,7 +34897,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="155" ht="35" spans="1:5">
+    <row r="155" ht="37.5" spans="1:5">
       <c r="A155" s="1">
         <v>24</v>
       </c>
@@ -34917,7 +34914,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="156" ht="35" spans="1:5">
+    <row r="156" ht="37.5" spans="1:5">
       <c r="A156" s="1">
         <v>25</v>
       </c>
@@ -34934,7 +34931,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="157" ht="35" spans="1:5">
+    <row r="157" ht="37.5" spans="1:5">
       <c r="A157" s="1">
         <v>26</v>
       </c>
@@ -34951,7 +34948,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="158" ht="35" spans="1:5">
+    <row r="158" ht="37.5" spans="1:5">
       <c r="A158" s="1">
         <v>27</v>
       </c>
@@ -34968,7 +34965,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="159" ht="35" spans="1:5">
+    <row r="159" ht="37.5" spans="1:5">
       <c r="A159" s="1">
         <v>28</v>
       </c>
@@ -34985,7 +34982,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="160" ht="35" spans="1:5">
+    <row r="160" ht="37.5" spans="1:5">
       <c r="A160" s="1">
         <v>29</v>
       </c>
@@ -35002,7 +34999,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="161" ht="35" spans="1:5">
+    <row r="161" ht="37.5" spans="1:5">
       <c r="A161" s="1">
         <v>30</v>
       </c>
@@ -35019,7 +35016,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="162" ht="35" spans="1:5">
+    <row r="162" ht="37.5" spans="1:5">
       <c r="A162" s="1">
         <v>31</v>
       </c>
@@ -35036,7 +35033,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="163" ht="35" spans="1:5">
+    <row r="163" ht="37.5" spans="1:5">
       <c r="A163" s="1">
         <v>32</v>
       </c>
@@ -35053,7 +35050,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="164" ht="35" spans="1:5">
+    <row r="164" ht="37.5" spans="1:5">
       <c r="A164" s="1">
         <v>33</v>
       </c>
@@ -35070,7 +35067,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="165" ht="35" spans="1:5">
+    <row r="165" ht="37.5" spans="1:5">
       <c r="A165" s="1">
         <v>34</v>
       </c>
@@ -35087,7 +35084,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="166" ht="35" spans="1:5">
+    <row r="166" ht="37.5" spans="1:5">
       <c r="A166" s="1">
         <v>35</v>
       </c>
@@ -35104,7 +35101,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="167" ht="35" spans="1:5">
+    <row r="167" ht="37.5" spans="1:5">
       <c r="A167" s="1">
         <v>36</v>
       </c>
@@ -35121,7 +35118,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="168" ht="35" spans="1:5">
+    <row r="168" ht="37.5" spans="1:5">
       <c r="A168" s="1">
         <v>37</v>
       </c>
@@ -35138,7 +35135,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="169" ht="35" spans="1:5">
+    <row r="169" ht="37.5" spans="1:5">
       <c r="A169" s="1">
         <v>38</v>
       </c>
@@ -35155,7 +35152,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="170" ht="35" spans="1:5">
+    <row r="170" ht="37.5" spans="1:5">
       <c r="A170" s="1">
         <v>39</v>
       </c>
@@ -35172,7 +35169,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="171" ht="35" spans="1:5">
+    <row r="171" ht="37.5" spans="1:5">
       <c r="A171" s="1">
         <v>40</v>
       </c>
@@ -35189,7 +35186,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="172" ht="35" spans="1:5">
+    <row r="172" ht="37.5" spans="1:5">
       <c r="A172" s="1">
         <v>41</v>
       </c>
@@ -35206,7 +35203,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="173" ht="35" spans="1:5">
+    <row r="173" ht="37.5" spans="1:5">
       <c r="A173" s="1">
         <v>42</v>
       </c>
@@ -35223,7 +35220,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="174" ht="35" spans="1:5">
+    <row r="174" ht="37.5" spans="1:5">
       <c r="A174" s="1">
         <v>43</v>
       </c>
@@ -35240,7 +35237,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="175" ht="35" spans="1:5">
+    <row r="175" ht="37.5" spans="1:5">
       <c r="A175" s="1">
         <v>44</v>
       </c>
@@ -35257,7 +35254,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="176" ht="35" spans="1:5">
+    <row r="176" ht="37.5" spans="1:5">
       <c r="A176" s="1">
         <v>45</v>
       </c>
@@ -35274,7 +35271,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="177" ht="35" spans="1:5">
+    <row r="177" ht="37.5" spans="1:5">
       <c r="A177" s="1">
         <v>46</v>
       </c>
@@ -35291,7 +35288,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="178" ht="35" spans="1:5">
+    <row r="178" ht="37.5" spans="1:5">
       <c r="A178" s="1">
         <v>47</v>
       </c>
@@ -35308,7 +35305,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="179" ht="35" spans="1:5">
+    <row r="179" ht="37.5" spans="1:5">
       <c r="A179" s="1">
         <v>48</v>
       </c>
@@ -35325,7 +35322,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="180" ht="35" spans="1:5">
+    <row r="180" ht="37.5" spans="1:5">
       <c r="A180" s="1">
         <v>49</v>
       </c>
@@ -35342,7 +35339,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="181" ht="35" spans="1:5">
+    <row r="181" ht="37.5" spans="1:5">
       <c r="A181" s="1">
         <v>50</v>
       </c>
@@ -35359,7 +35356,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="182" ht="35" spans="1:5">
+    <row r="182" ht="37.5" spans="1:5">
       <c r="A182" s="1">
         <v>51</v>
       </c>
@@ -35376,7 +35373,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="183" ht="35" spans="1:5">
+    <row r="183" ht="37.5" spans="1:5">
       <c r="A183" s="1">
         <v>52</v>
       </c>
@@ -35393,7 +35390,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="184" ht="35" spans="1:5">
+    <row r="184" ht="37.5" spans="1:5">
       <c r="A184" s="1">
         <v>53</v>
       </c>
@@ -35410,7 +35407,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="185" ht="35" spans="1:5">
+    <row r="185" ht="37.5" spans="1:5">
       <c r="A185" s="1">
         <v>54</v>
       </c>
@@ -35427,7 +35424,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="186" ht="35" spans="1:5">
+    <row r="186" ht="37.5" spans="1:5">
       <c r="A186" s="1">
         <v>55</v>
       </c>
@@ -35444,7 +35441,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="187" ht="35" spans="1:5">
+    <row r="187" ht="37.5" spans="1:5">
       <c r="A187" s="1">
         <v>56</v>
       </c>
@@ -35461,7 +35458,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="188" ht="35" spans="1:5">
+    <row r="188" ht="37.5" spans="1:5">
       <c r="A188" s="1">
         <v>57</v>
       </c>
@@ -35478,7 +35475,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="189" ht="35" spans="1:5">
+    <row r="189" ht="37.5" spans="1:5">
       <c r="A189" s="1">
         <v>58</v>
       </c>
@@ -35495,7 +35492,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="190" ht="35" spans="1:5">
+    <row r="190" ht="37.5" spans="1:5">
       <c r="A190" s="1">
         <v>59</v>
       </c>
@@ -35512,7 +35509,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="191" ht="35" spans="1:5">
+    <row r="191" ht="37.5" spans="1:5">
       <c r="A191" s="1">
         <v>62</v>
       </c>
@@ -35529,7 +35526,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="192" ht="35" spans="1:5">
+    <row r="192" ht="37.5" spans="1:5">
       <c r="A192" s="1">
         <v>63</v>
       </c>
@@ -35546,7 +35543,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="193" ht="35" spans="1:5">
+    <row r="193" ht="37.5" spans="1:5">
       <c r="A193" s="1">
         <v>64</v>
       </c>
@@ -35563,7 +35560,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="194" ht="35" spans="1:5">
+    <row r="194" ht="37.5" spans="1:5">
       <c r="A194" s="1">
         <v>65</v>
       </c>
@@ -35580,7 +35577,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="195" ht="35" spans="1:5">
+    <row r="195" ht="37.5" spans="1:5">
       <c r="A195" s="1">
         <v>66</v>
       </c>
